--- a/data/trans_orig/P1002-Provincia-trans_orig.xlsx
+++ b/data/trans_orig/P1002-Provincia-trans_orig.xlsx
@@ -538,7 +538,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que dejo de hacer algunas tareas por problemas emocionales en 2007</t>
+          <t>Población que dejo de hacer algunas tareas por problemas emocionales en 2007 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -733,12 +733,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>12750</t>
+          <t>12616</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>30386</t>
+          <t>29423</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -748,12 +748,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>4,67%</t>
+          <t>4,62%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>11,13%</t>
+          <t>10,78%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>12653</t>
+          <t>12968</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>30846</t>
+          <t>31419</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -783,12 +783,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>4,85%</t>
+          <t>4,97%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>11,83%</t>
+          <t>12,05%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>28810</t>
+          <t>29874</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>54562</t>
+          <t>54318</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>5,4%</t>
+          <t>5,6%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>10,22%</t>
+          <t>10,17%</t>
         </is>
       </c>
     </row>
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>242624</t>
+          <t>243587</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>260260</t>
+          <t>260394</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -861,12 +861,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>88,87%</t>
+          <t>89,22%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>95,33%</t>
+          <t>95,38%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -881,12 +881,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>229992</t>
+          <t>229419</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>248185</t>
+          <t>247870</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -896,12 +896,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>88,17%</t>
+          <t>87,95%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>95,15%</t>
+          <t>95,03%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>479286</t>
+          <t>479530</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>505038</t>
+          <t>503974</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>89,78%</t>
+          <t>89,83%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>94,6%</t>
+          <t>94,4%</t>
         </is>
       </c>
     </row>
@@ -1076,12 +1076,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>25593</t>
+          <t>25582</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>50664</t>
+          <t>49455</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1096,7 +1096,7 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>10,28%</t>
+          <t>10,03%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1111,12 +1111,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>59788</t>
+          <t>59228</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>91095</t>
+          <t>92921</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1126,12 +1126,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>11,86%</t>
+          <t>11,75%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>18,08%</t>
+          <t>18,44%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1146,12 +1146,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>90176</t>
+          <t>91444</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>128925</t>
+          <t>130716</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1161,12 +1161,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>9,04%</t>
+          <t>9,17%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>12,93%</t>
+          <t>13,11%</t>
         </is>
       </c>
     </row>
@@ -1189,12 +1189,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>442411</t>
+          <t>443620</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>467482</t>
+          <t>467493</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1204,7 +1204,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>89,72%</t>
+          <t>89,97%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -1224,12 +1224,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>412854</t>
+          <t>411028</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>444161</t>
+          <t>444721</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1239,12 +1239,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>81,92%</t>
+          <t>81,56%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>88,14%</t>
+          <t>88,25%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>868099</t>
+          <t>866308</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>906848</t>
+          <t>905580</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,12 +1274,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>87,07%</t>
+          <t>86,89%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>90,96%</t>
+          <t>90,83%</t>
         </is>
       </c>
     </row>
@@ -1419,12 +1419,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>944</t>
+          <t>942</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>10911</t>
+          <t>11467</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1439,7 +1439,7 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>3,42%</t>
+          <t>3,6%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1454,12 +1454,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>6304</t>
+          <t>6449</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>20805</t>
+          <t>20927</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1469,12 +1469,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>1,88%</t>
+          <t>1,92%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>6,2%</t>
+          <t>6,24%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1489,12 +1489,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>8962</t>
+          <t>8931</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>24775</t>
+          <t>25374</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1509,7 +1509,7 @@
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>3,79%</t>
+          <t>3,88%</t>
         </is>
       </c>
     </row>
@@ -1532,12 +1532,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>307935</t>
+          <t>307379</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>317902</t>
+          <t>317904</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1547,7 +1547,7 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>96,58%</t>
+          <t>96,4%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
@@ -1567,12 +1567,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>314607</t>
+          <t>314485</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>329108</t>
+          <t>328963</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1582,12 +1582,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>93,8%</t>
+          <t>93,76%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>98,12%</t>
+          <t>98,08%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1602,12 +1602,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>629483</t>
+          <t>628884</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>645296</t>
+          <t>645327</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1617,7 +1617,7 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>96,21%</t>
+          <t>96,12%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
@@ -1762,12 +1762,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>2566</t>
+          <t>2634</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>13360</t>
+          <t>12553</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1777,12 +1777,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>0,72%</t>
+          <t>0,73%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>3,72%</t>
+          <t>3,5%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1797,12 +1797,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>16294</t>
+          <t>16735</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>37497</t>
+          <t>35791</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1812,12 +1812,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>4,39%</t>
+          <t>4,51%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>10,09%</t>
+          <t>9,64%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1832,12 +1832,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>21651</t>
+          <t>21335</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>45186</t>
+          <t>43397</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1847,12 +1847,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>2,97%</t>
+          <t>2,92%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>6,19%</t>
+          <t>5,94%</t>
         </is>
       </c>
     </row>
@@ -1875,12 +1875,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>345311</t>
+          <t>346118</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>356105</t>
+          <t>356037</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1890,12 +1890,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>96,28%</t>
+          <t>96,5%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>99,28%</t>
+          <t>99,27%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1910,12 +1910,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>333959</t>
+          <t>335665</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>355162</t>
+          <t>354721</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1925,12 +1925,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>89,91%</t>
+          <t>90,36%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>95,61%</t>
+          <t>95,49%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>684941</t>
+          <t>686730</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>708476</t>
+          <t>708792</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1960,12 +1960,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>93,81%</t>
+          <t>94,06%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>97,03%</t>
+          <t>97,08%</t>
         </is>
       </c>
     </row>
@@ -2105,12 +2105,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>7589</t>
+          <t>7533</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>20012</t>
+          <t>20335</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2120,12 +2120,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>3,73%</t>
+          <t>3,71%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>9,84%</t>
+          <t>10,0%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2140,12 +2140,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>6887</t>
+          <t>6117</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>20859</t>
+          <t>19728</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2155,12 +2155,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>3,32%</t>
+          <t>2,95%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>10,04%</t>
+          <t>9,5%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2175,12 +2175,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>16217</t>
+          <t>16513</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>35633</t>
+          <t>35513</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2190,12 +2190,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>3,95%</t>
+          <t>4,02%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>8,67%</t>
+          <t>8,64%</t>
         </is>
       </c>
     </row>
@@ -2218,12 +2218,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>183296</t>
+          <t>182973</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>195719</t>
+          <t>195775</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2233,12 +2233,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>90,16%</t>
+          <t>90,0%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>96,27%</t>
+          <t>96,29%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2253,12 +2253,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>186809</t>
+          <t>187940</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>200781</t>
+          <t>201551</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2268,12 +2268,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>89,96%</t>
+          <t>90,5%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>96,68%</t>
+          <t>97,05%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2288,12 +2288,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>375343</t>
+          <t>375463</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>394759</t>
+          <t>394463</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2303,12 +2303,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>91,33%</t>
+          <t>91,36%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>96,05%</t>
+          <t>95,98%</t>
         </is>
       </c>
     </row>
@@ -2448,12 +2448,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>884</t>
+          <t>878</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>9967</t>
+          <t>8586</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2463,12 +2463,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>0,33%</t>
+          <t>0,32%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>3,68%</t>
+          <t>3,17%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2483,12 +2483,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>5116</t>
+          <t>5496</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>17929</t>
+          <t>18712</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2498,12 +2498,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>1,84%</t>
+          <t>1,98%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>6,45%</t>
+          <t>6,73%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2518,12 +2518,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>8148</t>
+          <t>7554</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>22772</t>
+          <t>22376</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2533,12 +2533,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>1,48%</t>
+          <t>1,38%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>4,15%</t>
+          <t>4,08%</t>
         </is>
       </c>
     </row>
@@ -2561,12 +2561,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>260844</t>
+          <t>262225</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>269927</t>
+          <t>269933</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2576,12 +2576,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>96,32%</t>
+          <t>96,83%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>99,67%</t>
+          <t>99,68%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2596,12 +2596,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>260215</t>
+          <t>259432</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>273028</t>
+          <t>272648</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2611,12 +2611,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>93,55%</t>
+          <t>93,27%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>98,16%</t>
+          <t>98,02%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2631,12 +2631,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>526183</t>
+          <t>526579</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>540807</t>
+          <t>541401</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2646,12 +2646,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>95,85%</t>
+          <t>95,92%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>98,52%</t>
+          <t>98,62%</t>
         </is>
       </c>
     </row>
@@ -2791,12 +2791,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>21970</t>
+          <t>21442</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>43966</t>
+          <t>44437</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2806,12 +2806,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>3,57%</t>
+          <t>3,49%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>7,15%</t>
+          <t>7,23%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2826,12 +2826,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>45553</t>
+          <t>47493</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>76295</t>
+          <t>75575</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2841,12 +2841,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>7,14%</t>
+          <t>7,44%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>11,95%</t>
+          <t>11,84%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2861,12 +2861,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>75371</t>
+          <t>74805</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>112595</t>
+          <t>110299</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2876,12 +2876,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>6,01%</t>
+          <t>5,97%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>8,98%</t>
+          <t>8,8%</t>
         </is>
       </c>
     </row>
@@ -2904,12 +2904,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>571061</t>
+          <t>570590</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>593057</t>
+          <t>593585</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2919,12 +2919,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>92,85%</t>
+          <t>92,77%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>96,43%</t>
+          <t>96,51%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2939,12 +2939,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>561924</t>
+          <t>562644</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>592666</t>
+          <t>590726</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2954,12 +2954,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>88,05%</t>
+          <t>88,16%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>92,86%</t>
+          <t>92,56%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2974,12 +2974,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>1140651</t>
+          <t>1142947</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>1177875</t>
+          <t>1178441</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2989,12 +2989,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>91,02%</t>
+          <t>91,2%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>93,99%</t>
+          <t>94,03%</t>
         </is>
       </c>
     </row>
@@ -3134,12 +3134,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>44060</t>
+          <t>44095</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>72323</t>
+          <t>73711</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3149,12 +3149,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>5,92%</t>
+          <t>5,93%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>9,72%</t>
+          <t>9,91%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3169,12 +3169,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>57035</t>
+          <t>56905</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>89178</t>
+          <t>88992</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3184,12 +3184,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>7,28%</t>
+          <t>7,26%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>11,38%</t>
+          <t>11,36%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3204,12 +3204,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>108996</t>
+          <t>110203</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>153440</t>
+          <t>155330</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3219,12 +3219,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>7,14%</t>
+          <t>7,22%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>10,05%</t>
+          <t>10,17%</t>
         </is>
       </c>
     </row>
@@ -3247,12 +3247,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>671472</t>
+          <t>670084</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>699735</t>
+          <t>699700</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3262,12 +3262,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>90,28%</t>
+          <t>90,09%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>94,08%</t>
+          <t>94,07%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3282,12 +3282,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>694333</t>
+          <t>694519</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>726476</t>
+          <t>726606</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3297,12 +3297,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>88,62%</t>
+          <t>88,64%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>92,72%</t>
+          <t>92,74%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3317,12 +3317,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>1373866</t>
+          <t>1371976</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>1418310</t>
+          <t>1417103</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3332,12 +3332,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>89,95%</t>
+          <t>89,83%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>92,86%</t>
+          <t>92,78%</t>
         </is>
       </c>
     </row>
@@ -3477,12 +3477,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>146413</t>
+          <t>146756</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>197135</t>
+          <t>198797</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -3492,12 +3492,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>4,47%</t>
+          <t>4,48%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>6,02%</t>
+          <t>6,07%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -3512,12 +3512,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>253234</t>
+          <t>254321</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>321680</t>
+          <t>320284</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -3527,12 +3527,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>7,49%</t>
+          <t>7,53%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>9,52%</t>
+          <t>9,48%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3547,12 +3547,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>416591</t>
+          <t>416760</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>501248</t>
+          <t>498152</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -3567,7 +3567,7 @@
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>7,53%</t>
+          <t>7,48%</t>
         </is>
       </c>
     </row>
@@ -3590,12 +3590,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>3079408</t>
+          <t>3077746</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>3130130</t>
+          <t>3129787</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -3605,12 +3605,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>93,98%</t>
+          <t>93,93%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>95,53%</t>
+          <t>95,52%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -3625,12 +3625,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>3057517</t>
+          <t>3058913</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>3125963</t>
+          <t>3124876</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -3640,12 +3640,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>90,48%</t>
+          <t>90,52%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>92,51%</t>
+          <t>92,47%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3660,12 +3660,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>6154493</t>
+          <t>6157589</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>6239150</t>
+          <t>6238981</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -3675,7 +3675,7 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>92,47%</t>
+          <t>92,52%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
@@ -3861,7 +3861,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que dejo de hacer algunas tareas por problemas emocionales en 2012</t>
+          <t>Población que dejo de hacer algunas tareas por problemas emocionales en 2012 (tasa de respuesta: 99,94%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -4056,12 +4056,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>16823</t>
+          <t>17369</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>37439</t>
+          <t>37268</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -4071,12 +4071,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>5,71%</t>
+          <t>5,89%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>12,7%</t>
+          <t>12,64%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -4091,12 +4091,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>44644</t>
+          <t>43907</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>71675</t>
+          <t>71759</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -4106,12 +4106,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>15,54%</t>
+          <t>15,29%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>24,95%</t>
+          <t>24,98%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -4126,12 +4126,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>67343</t>
+          <t>67437</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>100875</t>
+          <t>102271</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -4141,12 +4141,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>11,57%</t>
+          <t>11,59%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>17,33%</t>
+          <t>17,57%</t>
         </is>
       </c>
     </row>
@@ -4169,12 +4169,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>257299</t>
+          <t>257470</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>277915</t>
+          <t>277369</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -4184,12 +4184,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>87,3%</t>
+          <t>87,36%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>94,29%</t>
+          <t>94,11%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -4204,12 +4204,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>215570</t>
+          <t>215486</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>242601</t>
+          <t>243338</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -4219,12 +4219,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>75,05%</t>
+          <t>75,02%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>84,46%</t>
+          <t>84,71%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -4239,12 +4239,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>481108</t>
+          <t>479712</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>514640</t>
+          <t>514546</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -4254,12 +4254,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>82,67%</t>
+          <t>82,43%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>88,43%</t>
+          <t>88,41%</t>
         </is>
       </c>
     </row>
@@ -4399,12 +4399,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>28302</t>
+          <t>27286</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>55498</t>
+          <t>54452</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4414,12 +4414,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>5,6%</t>
+          <t>5,4%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>10,98%</t>
+          <t>10,77%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -4434,12 +4434,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>61182</t>
+          <t>61071</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>96640</t>
+          <t>95859</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -4449,12 +4449,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>11,7%</t>
+          <t>11,68%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>18,49%</t>
+          <t>18,34%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -4469,12 +4469,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>95410</t>
+          <t>98266</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>140238</t>
+          <t>140918</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -4484,12 +4484,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>9,28%</t>
+          <t>9,56%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>13,64%</t>
+          <t>13,7%</t>
         </is>
       </c>
     </row>
@@ -4512,12 +4512,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>450029</t>
+          <t>451075</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>477225</t>
+          <t>478241</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -4527,12 +4527,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>89,02%</t>
+          <t>89,23%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>94,4%</t>
+          <t>94,6%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -4547,12 +4547,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>426070</t>
+          <t>426851</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>461528</t>
+          <t>461639</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -4562,12 +4562,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>81,51%</t>
+          <t>81,66%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>88,3%</t>
+          <t>88,32%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -4582,12 +4582,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>887999</t>
+          <t>887319</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>932827</t>
+          <t>929971</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -4597,12 +4597,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>86,36%</t>
+          <t>86,3%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>90,72%</t>
+          <t>90,44%</t>
         </is>
       </c>
     </row>
@@ -4742,12 +4742,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>10731</t>
+          <t>11164</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>27984</t>
+          <t>28847</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -4757,12 +4757,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>3,31%</t>
+          <t>3,45%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>8,64%</t>
+          <t>8,9%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -4777,12 +4777,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>26638</t>
+          <t>26960</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>51864</t>
+          <t>51268</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -4792,12 +4792,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>7,81%</t>
+          <t>7,91%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>15,21%</t>
+          <t>15,03%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -4812,12 +4812,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>42755</t>
+          <t>42075</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>73405</t>
+          <t>72713</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4827,12 +4827,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>6,43%</t>
+          <t>6,33%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>11,04%</t>
+          <t>10,93%</t>
         </is>
       </c>
     </row>
@@ -4855,12 +4855,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>296062</t>
+          <t>295199</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>313315</t>
+          <t>312882</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -4870,12 +4870,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>91,36%</t>
+          <t>91,1%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>96,69%</t>
+          <t>96,55%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -4890,12 +4890,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>289156</t>
+          <t>289752</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>314382</t>
+          <t>314060</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -4905,12 +4905,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>84,79%</t>
+          <t>84,97%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>92,19%</t>
+          <t>92,09%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -4925,12 +4925,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>591661</t>
+          <t>592353</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>622311</t>
+          <t>622991</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -4940,12 +4940,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>88,96%</t>
+          <t>89,07%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>93,57%</t>
+          <t>93,67%</t>
         </is>
       </c>
     </row>
@@ -5085,12 +5085,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>15093</t>
+          <t>14798</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>34496</t>
+          <t>33946</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -5100,12 +5100,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>4,04%</t>
+          <t>3,96%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>9,22%</t>
+          <t>9,08%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -5120,12 +5120,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>64545</t>
+          <t>65771</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>95846</t>
+          <t>96924</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -5135,12 +5135,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>16,59%</t>
+          <t>16,91%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>24,64%</t>
+          <t>24,92%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5155,12 +5155,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>85916</t>
+          <t>87187</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>123892</t>
+          <t>124140</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5170,12 +5170,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>11,26%</t>
+          <t>11,43%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>16,24%</t>
+          <t>16,27%</t>
         </is>
       </c>
     </row>
@@ -5198,12 +5198,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>339486</t>
+          <t>340036</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>358889</t>
+          <t>359184</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -5213,12 +5213,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>90,78%</t>
+          <t>90,92%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>95,96%</t>
+          <t>96,04%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -5233,12 +5233,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>293105</t>
+          <t>292027</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>324406</t>
+          <t>323180</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -5248,12 +5248,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>75,36%</t>
+          <t>75,08%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>83,41%</t>
+          <t>83,09%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -5268,12 +5268,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>639041</t>
+          <t>638793</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>677017</t>
+          <t>675746</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -5283,12 +5283,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>83,76%</t>
+          <t>83,73%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>88,74%</t>
+          <t>88,57%</t>
         </is>
       </c>
     </row>
@@ -5428,12 +5428,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>4765</t>
+          <t>4324</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>17125</t>
+          <t>16662</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -5443,12 +5443,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>2,24%</t>
+          <t>2,03%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>8,05%</t>
+          <t>7,84%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -5463,12 +5463,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>27718</t>
+          <t>27652</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>50062</t>
+          <t>50417</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -5478,12 +5478,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>12,62%</t>
+          <t>12,59%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>22,8%</t>
+          <t>22,96%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -5498,12 +5498,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>35681</t>
+          <t>35219</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>62217</t>
+          <t>60456</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -5513,12 +5513,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>8,26%</t>
+          <t>8,15%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>14,4%</t>
+          <t>13,99%</t>
         </is>
       </c>
     </row>
@@ -5541,12 +5541,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>195493</t>
+          <t>195956</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>207853</t>
+          <t>208294</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -5556,12 +5556,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>91,95%</t>
+          <t>92,16%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>97,76%</t>
+          <t>97,97%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -5576,12 +5576,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>169529</t>
+          <t>169174</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>191873</t>
+          <t>191939</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -5591,12 +5591,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>77,2%</t>
+          <t>77,04%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>87,38%</t>
+          <t>87,41%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -5611,12 +5611,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>369992</t>
+          <t>371753</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>396528</t>
+          <t>396990</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -5626,12 +5626,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>85,6%</t>
+          <t>86,01%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>91,74%</t>
+          <t>91,85%</t>
         </is>
       </c>
     </row>
@@ -5771,12 +5771,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>12183</t>
+          <t>11503</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>28219</t>
+          <t>29105</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -5786,12 +5786,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>4,46%</t>
+          <t>4,21%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>10,34%</t>
+          <t>10,66%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -5806,12 +5806,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>19319</t>
+          <t>20668</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>41593</t>
+          <t>40424</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -5821,12 +5821,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>6,9%</t>
+          <t>7,38%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>14,85%</t>
+          <t>14,44%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -5841,12 +5841,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>36407</t>
+          <t>38232</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>62514</t>
+          <t>62162</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -5856,12 +5856,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>6,58%</t>
+          <t>6,91%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>11,31%</t>
+          <t>11,24%</t>
         </is>
       </c>
     </row>
@@ -5884,12 +5884,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>244708</t>
+          <t>243822</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>260744</t>
+          <t>261424</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -5899,12 +5899,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>89,66%</t>
+          <t>89,34%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>95,54%</t>
+          <t>95,79%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -5919,12 +5919,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>238438</t>
+          <t>239607</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>260712</t>
+          <t>259363</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -5934,12 +5934,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>85,15%</t>
+          <t>85,56%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>93,1%</t>
+          <t>92,62%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -5954,12 +5954,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>490444</t>
+          <t>490796</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>516551</t>
+          <t>514726</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -5969,12 +5969,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>88,69%</t>
+          <t>88,76%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>93,42%</t>
+          <t>93,09%</t>
         </is>
       </c>
     </row>
@@ -6114,12 +6114,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>18442</t>
+          <t>18117</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>41586</t>
+          <t>40302</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -6129,12 +6129,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>2,78%</t>
+          <t>2,73%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>6,27%</t>
+          <t>6,08%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -6149,12 +6149,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>38892</t>
+          <t>37850</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>68220</t>
+          <t>66858</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -6164,12 +6164,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>5,61%</t>
+          <t>5,46%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>9,85%</t>
+          <t>9,65%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -6184,12 +6184,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>63450</t>
+          <t>63301</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>99378</t>
+          <t>99140</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -6199,12 +6199,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>4,68%</t>
+          <t>4,67%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>7,33%</t>
+          <t>7,31%</t>
         </is>
       </c>
     </row>
@@ -6227,12 +6227,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>621202</t>
+          <t>622486</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>644346</t>
+          <t>644671</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -6242,12 +6242,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>93,73%</t>
+          <t>93,92%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>97,22%</t>
+          <t>97,27%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -6262,12 +6262,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>624688</t>
+          <t>626050</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>654016</t>
+          <t>655058</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -6277,12 +6277,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>90,15%</t>
+          <t>90,35%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>94,39%</t>
+          <t>94,54%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -6297,12 +6297,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>1256318</t>
+          <t>1256556</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>1292246</t>
+          <t>1292395</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -6312,12 +6312,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>92,67%</t>
+          <t>92,69%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>95,32%</t>
+          <t>95,33%</t>
         </is>
       </c>
     </row>
@@ -6457,12 +6457,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>50404</t>
+          <t>50133</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>85372</t>
+          <t>85490</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -6472,12 +6472,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>6,48%</t>
+          <t>6,44%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>10,97%</t>
+          <t>10,99%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -6492,12 +6492,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>105392</t>
+          <t>104440</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>147004</t>
+          <t>146397</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -6507,12 +6507,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>12,79%</t>
+          <t>12,68%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>17,84%</t>
+          <t>17,77%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -6527,12 +6527,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>167298</t>
+          <t>166998</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>220209</t>
+          <t>220993</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -6542,12 +6542,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>10,44%</t>
+          <t>10,42%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>13,75%</t>
+          <t>13,79%</t>
         </is>
       </c>
     </row>
@@ -6570,12 +6570,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>692789</t>
+          <t>692671</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>727757</t>
+          <t>728028</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -6585,12 +6585,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>89,03%</t>
+          <t>89,01%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>93,52%</t>
+          <t>93,56%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -6605,12 +6605,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>676849</t>
+          <t>677456</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>718461</t>
+          <t>719413</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -6620,12 +6620,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>82,16%</t>
+          <t>82,23%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>87,21%</t>
+          <t>87,32%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -6640,12 +6640,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>1381805</t>
+          <t>1381021</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>1434716</t>
+          <t>1435016</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -6655,12 +6655,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>86,25%</t>
+          <t>86,21%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>89,56%</t>
+          <t>89,58%</t>
         </is>
       </c>
     </row>
@@ -6800,12 +6800,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>202429</t>
+          <t>200223</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>265576</t>
+          <t>262762</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -6815,12 +6815,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>5,91%</t>
+          <t>5,85%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>7,75%</t>
+          <t>7,67%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -6835,12 +6835,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>458056</t>
+          <t>458486</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>540116</t>
+          <t>543955</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -6850,12 +6850,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>12,88%</t>
+          <t>12,89%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>15,19%</t>
+          <t>15,3%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -6870,12 +6870,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>674567</t>
+          <t>676277</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>780114</t>
+          <t>777108</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -6885,12 +6885,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>9,66%</t>
+          <t>9,69%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>11,17%</t>
+          <t>11,13%</t>
         </is>
       </c>
     </row>
@@ -6913,12 +6913,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>3159212</t>
+          <t>3162026</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>3222359</t>
+          <t>3224565</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -6928,12 +6928,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>92,25%</t>
+          <t>92,33%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>94,09%</t>
+          <t>94,15%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -6948,12 +6948,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>3016193</t>
+          <t>3012354</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>3098253</t>
+          <t>3097823</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -6963,12 +6963,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>84,81%</t>
+          <t>84,7%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>87,12%</t>
+          <t>87,11%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -6983,12 +6983,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>6200983</t>
+          <t>6203989</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>6306530</t>
+          <t>6304820</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -6998,12 +6998,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>88,83%</t>
+          <t>88,87%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>90,34%</t>
+          <t>90,31%</t>
         </is>
       </c>
     </row>
@@ -7184,7 +7184,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que dejo de hacer algunas tareas por problemas emocionales en 2016</t>
+          <t>Población que dejo de hacer algunas tareas por problemas emocionales en 2016 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -7379,12 +7379,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>18035</t>
+          <t>18116</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>39790</t>
+          <t>39630</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -7394,12 +7394,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>6,14%</t>
+          <t>6,17%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>13,55%</t>
+          <t>13,49%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -7414,12 +7414,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>44477</t>
+          <t>44206</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>70154</t>
+          <t>72580</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -7429,12 +7429,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>15,41%</t>
+          <t>15,31%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>24,3%</t>
+          <t>25,14%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -7449,12 +7449,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>66228</t>
+          <t>66655</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>103305</t>
+          <t>101987</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -7464,12 +7464,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>11,37%</t>
+          <t>11,44%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>17,74%</t>
+          <t>17,51%</t>
         </is>
       </c>
     </row>
@@ -7492,12 +7492,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>253971</t>
+          <t>254131</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>275726</t>
+          <t>275645</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -7507,12 +7507,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>86,45%</t>
+          <t>86,51%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>93,86%</t>
+          <t>93,83%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -7527,12 +7527,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>218549</t>
+          <t>216123</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>244226</t>
+          <t>244497</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -7542,12 +7542,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>75,7%</t>
+          <t>74,86%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>84,59%</t>
+          <t>84,69%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -7562,12 +7562,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>479159</t>
+          <t>480477</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>516236</t>
+          <t>515809</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -7577,12 +7577,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>82,26%</t>
+          <t>82,49%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>88,63%</t>
+          <t>88,56%</t>
         </is>
       </c>
     </row>
@@ -7722,12 +7722,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>7189</t>
+          <t>7149</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>22123</t>
+          <t>21726</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -7737,12 +7737,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>1,43%</t>
+          <t>1,42%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>4,4%</t>
+          <t>4,32%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -7757,12 +7757,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>30444</t>
+          <t>31031</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>55750</t>
+          <t>56775</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -7772,12 +7772,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>5,82%</t>
+          <t>5,93%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>10,66%</t>
+          <t>10,85%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -7792,12 +7792,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>42747</t>
+          <t>41586</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>72530</t>
+          <t>72355</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -7807,12 +7807,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>4,17%</t>
+          <t>4,05%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>7,07%</t>
+          <t>7,05%</t>
         </is>
       </c>
     </row>
@@ -7835,12 +7835,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>480452</t>
+          <t>480849</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>495386</t>
+          <t>495426</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -7850,12 +7850,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>95,6%</t>
+          <t>95,68%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>98,57%</t>
+          <t>98,58%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -7870,12 +7870,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>467334</t>
+          <t>466309</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>492640</t>
+          <t>492053</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -7885,12 +7885,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>89,34%</t>
+          <t>89,15%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>94,18%</t>
+          <t>94,07%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -7905,12 +7905,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>953129</t>
+          <t>953304</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>982912</t>
+          <t>984073</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -7920,12 +7920,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>92,93%</t>
+          <t>92,95%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>95,83%</t>
+          <t>95,95%</t>
         </is>
       </c>
     </row>
@@ -8065,12 +8065,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>2992</t>
+          <t>3083</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>12911</t>
+          <t>13826</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -8080,12 +8080,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>0,94%</t>
+          <t>0,97%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>4,05%</t>
+          <t>4,34%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -8100,12 +8100,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>9492</t>
+          <t>10573</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>26057</t>
+          <t>27401</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -8115,12 +8115,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>2,82%</t>
+          <t>3,14%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>7,75%</t>
+          <t>8,15%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -8135,12 +8135,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>15762</t>
+          <t>14780</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>34788</t>
+          <t>34206</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -8150,12 +8150,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>2,41%</t>
+          <t>2,26%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>5,31%</t>
+          <t>5,22%</t>
         </is>
       </c>
     </row>
@@ -8178,12 +8178,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>305654</t>
+          <t>304739</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>315573</t>
+          <t>315482</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -8193,12 +8193,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>95,95%</t>
+          <t>95,66%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>99,06%</t>
+          <t>99,03%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -8213,12 +8213,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>310252</t>
+          <t>308908</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>326817</t>
+          <t>325736</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -8228,12 +8228,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>92,25%</t>
+          <t>91,85%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>97,18%</t>
+          <t>96,86%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -8248,12 +8248,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>620086</t>
+          <t>620668</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>639112</t>
+          <t>640094</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -8263,12 +8263,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>94,69%</t>
+          <t>94,78%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>97,59%</t>
+          <t>97,74%</t>
         </is>
       </c>
     </row>
@@ -8408,12 +8408,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>22851</t>
+          <t>21859</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>43187</t>
+          <t>43904</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -8423,12 +8423,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>6,18%</t>
+          <t>5,91%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>11,67%</t>
+          <t>11,87%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -8443,12 +8443,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>55662</t>
+          <t>57593</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>89737</t>
+          <t>90549</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -8458,12 +8458,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>14,37%</t>
+          <t>14,87%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>23,17%</t>
+          <t>23,38%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -8478,12 +8478,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>86141</t>
+          <t>84952</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>125131</t>
+          <t>126756</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -8493,12 +8493,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>11,38%</t>
+          <t>11,22%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>16,52%</t>
+          <t>16,74%</t>
         </is>
       </c>
     </row>
@@ -8521,12 +8521,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>326777</t>
+          <t>326060</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>347113</t>
+          <t>348105</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -8536,12 +8536,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>88,33%</t>
+          <t>88,13%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>93,82%</t>
+          <t>94,09%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -8556,12 +8556,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>297546</t>
+          <t>296734</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>331621</t>
+          <t>329690</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -8571,12 +8571,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>76,83%</t>
+          <t>76,62%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>85,63%</t>
+          <t>85,13%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -8591,12 +8591,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>632116</t>
+          <t>630491</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>671106</t>
+          <t>672295</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -8606,12 +8606,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>83,48%</t>
+          <t>83,26%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>88,62%</t>
+          <t>88,78%</t>
         </is>
       </c>
     </row>
@@ -8751,12 +8751,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>3926</t>
+          <t>4026</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>15633</t>
+          <t>15814</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -8766,12 +8766,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>1,86%</t>
+          <t>1,91%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>7,4%</t>
+          <t>7,49%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -8786,12 +8786,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>10566</t>
+          <t>11027</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>26940</t>
+          <t>27743</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -8801,12 +8801,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>4,83%</t>
+          <t>5,04%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>12,32%</t>
+          <t>12,69%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -8821,12 +8821,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>17878</t>
+          <t>17660</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>36879</t>
+          <t>38936</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -8836,12 +8836,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>4,16%</t>
+          <t>4,11%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>8,58%</t>
+          <t>9,06%</t>
         </is>
       </c>
     </row>
@@ -8864,12 +8864,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>195588</t>
+          <t>195407</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>207295</t>
+          <t>207195</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -8879,12 +8879,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>92,6%</t>
+          <t>92,51%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>98,14%</t>
+          <t>98,09%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -8899,12 +8899,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>191647</t>
+          <t>190844</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>208021</t>
+          <t>207560</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -8914,12 +8914,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>87,68%</t>
+          <t>87,31%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>95,17%</t>
+          <t>94,96%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -8934,12 +8934,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>392929</t>
+          <t>390872</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>411930</t>
+          <t>412148</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -8949,12 +8949,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>91,42%</t>
+          <t>90,94%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>95,84%</t>
+          <t>95,89%</t>
         </is>
       </c>
     </row>
@@ -9094,12 +9094,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>12615</t>
+          <t>13542</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>30768</t>
+          <t>31765</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -9109,12 +9109,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>4,79%</t>
+          <t>5,15%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>11,69%</t>
+          <t>12,07%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -9129,12 +9129,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>23667</t>
+          <t>25260</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>46421</t>
+          <t>48064</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -9144,12 +9144,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>8,67%</t>
+          <t>9,25%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>17,0%</t>
+          <t>17,6%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -9164,12 +9164,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>40959</t>
+          <t>40532</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>73018</t>
+          <t>69692</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -9179,12 +9179,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>7,64%</t>
+          <t>7,56%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>13,62%</t>
+          <t>13,0%</t>
         </is>
       </c>
     </row>
@@ -9207,12 +9207,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>232355</t>
+          <t>231358</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>250508</t>
+          <t>249581</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -9222,12 +9222,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>88,31%</t>
+          <t>87,93%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>95,21%</t>
+          <t>94,85%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -9242,12 +9242,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>226694</t>
+          <t>225051</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>249448</t>
+          <t>247855</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -9257,12 +9257,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>83,0%</t>
+          <t>82,4%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>91,33%</t>
+          <t>90,75%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -9277,12 +9277,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>463220</t>
+          <t>466546</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>495279</t>
+          <t>495706</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -9292,12 +9292,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>86,38%</t>
+          <t>87,0%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>92,36%</t>
+          <t>92,44%</t>
         </is>
       </c>
     </row>
@@ -9437,12 +9437,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>28405</t>
+          <t>28688</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>56860</t>
+          <t>55172</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -9452,12 +9452,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>4,33%</t>
+          <t>4,37%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>8,66%</t>
+          <t>8,4%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -9472,12 +9472,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>65756</t>
+          <t>64632</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>102511</t>
+          <t>100284</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -9487,12 +9487,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>9,51%</t>
+          <t>9,35%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>14,83%</t>
+          <t>14,51%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -9507,12 +9507,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>101353</t>
+          <t>101439</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>147866</t>
+          <t>145134</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -9522,12 +9522,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>7,52%</t>
+          <t>7,53%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>10,97%</t>
+          <t>10,77%</t>
         </is>
       </c>
     </row>
@@ -9550,12 +9550,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>599698</t>
+          <t>601386</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>628153</t>
+          <t>627870</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -9565,12 +9565,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>91,34%</t>
+          <t>91,6%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>95,67%</t>
+          <t>95,63%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -9585,12 +9585,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>588783</t>
+          <t>591010</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>625538</t>
+          <t>626662</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -9600,12 +9600,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>85,17%</t>
+          <t>85,49%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>90,49%</t>
+          <t>90,65%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -9620,12 +9620,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>1199986</t>
+          <t>1202718</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>1246499</t>
+          <t>1246413</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -9635,12 +9635,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>89,03%</t>
+          <t>89,23%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>92,48%</t>
+          <t>92,47%</t>
         </is>
       </c>
     </row>
@@ -9780,12 +9780,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>22864</t>
+          <t>22650</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>44128</t>
+          <t>44029</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -9795,12 +9795,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>2,94%</t>
+          <t>2,91%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>5,67%</t>
+          <t>5,66%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -9815,12 +9815,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>41996</t>
+          <t>42652</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>72978</t>
+          <t>73945</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -9830,12 +9830,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>5,08%</t>
+          <t>5,16%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>8,83%</t>
+          <t>8,95%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -9850,12 +9850,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>72328</t>
+          <t>71772</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>111141</t>
+          <t>110584</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -9865,12 +9865,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>4,51%</t>
+          <t>4,47%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>6,93%</t>
+          <t>6,89%</t>
         </is>
       </c>
     </row>
@@ -9893,12 +9893,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>734455</t>
+          <t>734554</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>755719</t>
+          <t>755933</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -9908,12 +9908,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>94,33%</t>
+          <t>94,34%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>97,06%</t>
+          <t>97,09%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -9928,12 +9928,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>753189</t>
+          <t>752222</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>784171</t>
+          <t>783515</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -9943,12 +9943,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>91,17%</t>
+          <t>91,05%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>94,92%</t>
+          <t>94,84%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -9963,12 +9963,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>1493609</t>
+          <t>1494166</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>1532422</t>
+          <t>1532978</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -9978,12 +9978,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>93,07%</t>
+          <t>93,11%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>95,49%</t>
+          <t>95,53%</t>
         </is>
       </c>
     </row>
@@ -10123,12 +10123,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>157335</t>
+          <t>155036</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>209501</t>
+          <t>210026</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -10138,12 +10138,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>4,64%</t>
+          <t>4,57%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>6,17%</t>
+          <t>6,19%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -10158,12 +10158,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>341007</t>
+          <t>342362</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>415129</t>
+          <t>420308</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -10173,12 +10173,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>9,62%</t>
+          <t>9,66%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>11,71%</t>
+          <t>11,86%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -10193,12 +10193,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>512014</t>
+          <t>512495</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>603749</t>
+          <t>607279</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -10208,12 +10208,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>7,38%</t>
+          <t>7,39%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>8,7%</t>
+          <t>8,75%</t>
         </is>
       </c>
     </row>
@@ -10236,12 +10236,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>3184849</t>
+          <t>3184324</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>3237015</t>
+          <t>3239314</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -10251,12 +10251,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>93,83%</t>
+          <t>93,81%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>95,36%</t>
+          <t>95,43%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -10271,12 +10271,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>3129413</t>
+          <t>3124234</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>3203535</t>
+          <t>3202180</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -10286,12 +10286,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>88,29%</t>
+          <t>88,14%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>90,38%</t>
+          <t>90,34%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -10306,12 +10306,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>6335143</t>
+          <t>6331613</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>6426878</t>
+          <t>6426397</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -10321,12 +10321,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>91,3%</t>
+          <t>91,25%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>92,62%</t>
+          <t>92,61%</t>
         </is>
       </c>
     </row>
@@ -10507,7 +10507,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que dejo de hacer algunas tareas por problemas emocionales en 2023</t>
+          <t>Población que dejo de hacer algunas tareas por problemas emocionales en 2023 (tasa de respuesta: 99,93%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -10702,12 +10702,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>2292</t>
+          <t>2281</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>13295</t>
+          <t>14060</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -10717,12 +10717,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>0,74%</t>
+          <t>0,73%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>4,27%</t>
+          <t>4,51%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -10737,12 +10737,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>5152</t>
+          <t>5185</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>15034</t>
+          <t>15144</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -10752,12 +10752,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>1,78%</t>
+          <t>1,79%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>5,19%</t>
+          <t>5,23%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -10772,12 +10772,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>9209</t>
+          <t>9317</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>23614</t>
+          <t>23415</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -10787,12 +10787,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>1,53%</t>
+          <t>1,55%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>3,93%</t>
+          <t>3,9%</t>
         </is>
       </c>
     </row>
@@ -10815,12 +10815,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>298148</t>
+          <t>297383</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>309151</t>
+          <t>309162</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -10830,12 +10830,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>95,73%</t>
+          <t>95,49%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>99,26%</t>
+          <t>99,27%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -10850,12 +10850,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>274601</t>
+          <t>274491</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>284483</t>
+          <t>284450</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -10865,12 +10865,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>94,81%</t>
+          <t>94,77%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>98,22%</t>
+          <t>98,21%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -10885,12 +10885,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>577463</t>
+          <t>577662</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>591868</t>
+          <t>591760</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -10900,12 +10900,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>96,07%</t>
+          <t>96,1%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>98,47%</t>
+          <t>98,45%</t>
         </is>
       </c>
     </row>
@@ -11045,12 +11045,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>25084</t>
+          <t>23952</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>50237</t>
+          <t>50242</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -11060,7 +11060,7 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>4,84%</t>
+          <t>4,62%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
@@ -11080,12 +11080,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>44002</t>
+          <t>44937</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>68340</t>
+          <t>68852</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -11095,12 +11095,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>8,56%</t>
+          <t>8,74%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>13,29%</t>
+          <t>13,39%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -11115,12 +11115,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>74869</t>
+          <t>75798</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>109811</t>
+          <t>110677</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -11130,12 +11130,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>7,25%</t>
+          <t>7,34%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>10,63%</t>
+          <t>10,72%</t>
         </is>
       </c>
     </row>
@@ -11158,12 +11158,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>468153</t>
+          <t>468148</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>493306</t>
+          <t>494438</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -11178,7 +11178,7 @@
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>95,16%</t>
+          <t>95,38%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -11193,12 +11193,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>445982</t>
+          <t>445470</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>470320</t>
+          <t>469385</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -11208,12 +11208,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>86,71%</t>
+          <t>86,61%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>91,44%</t>
+          <t>91,26%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -11228,12 +11228,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>922901</t>
+          <t>922035</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>957843</t>
+          <t>956914</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -11243,12 +11243,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>89,37%</t>
+          <t>89,28%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>92,75%</t>
+          <t>92,66%</t>
         </is>
       </c>
     </row>
@@ -11388,12 +11388,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>11008</t>
+          <t>12047</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>25712</t>
+          <t>26993</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -11403,12 +11403,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>3,48%</t>
+          <t>3,81%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>8,14%</t>
+          <t>8,54%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -11423,12 +11423,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>16176</t>
+          <t>16584</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>30731</t>
+          <t>29677</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -11438,12 +11438,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>4,64%</t>
+          <t>4,76%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>8,82%</t>
+          <t>8,51%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -11458,12 +11458,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>31674</t>
+          <t>31129</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>50948</t>
+          <t>51571</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -11473,12 +11473,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>4,77%</t>
+          <t>4,68%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>7,67%</t>
+          <t>7,76%</t>
         </is>
       </c>
     </row>
@@ -11501,12 +11501,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>290338</t>
+          <t>289057</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>305042</t>
+          <t>304003</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -11516,12 +11516,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>91,86%</t>
+          <t>91,46%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>96,52%</t>
+          <t>96,19%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -11536,12 +11536,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>317837</t>
+          <t>318891</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>332392</t>
+          <t>331984</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -11551,12 +11551,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>91,18%</t>
+          <t>91,49%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>95,36%</t>
+          <t>95,24%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -11571,12 +11571,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>613670</t>
+          <t>613047</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>632944</t>
+          <t>633489</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -11586,12 +11586,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>92,33%</t>
+          <t>92,24%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>95,23%</t>
+          <t>95,32%</t>
         </is>
       </c>
     </row>
@@ -11731,12 +11731,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>10840</t>
+          <t>11256</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>27824</t>
+          <t>30000</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -11746,12 +11746,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>3,48%</t>
+          <t>3,62%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>8,94%</t>
+          <t>9,64%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -11766,12 +11766,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>24901</t>
+          <t>27027</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>60468</t>
+          <t>61882</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -11781,12 +11781,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>5,23%</t>
+          <t>5,68%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>12,71%</t>
+          <t>13,01%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -11801,12 +11801,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>44695</t>
+          <t>44429</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>83309</t>
+          <t>82092</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -11816,12 +11816,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>5,68%</t>
+          <t>5,64%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>10,58%</t>
+          <t>10,43%</t>
         </is>
       </c>
     </row>
@@ -11844,12 +11844,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>283526</t>
+          <t>281350</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>300510</t>
+          <t>300094</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -11859,12 +11859,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>91,06%</t>
+          <t>90,36%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>96,52%</t>
+          <t>96,38%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -11879,12 +11879,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>415250</t>
+          <t>413836</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>450817</t>
+          <t>448691</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -11894,12 +11894,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>87,29%</t>
+          <t>86,99%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>94,77%</t>
+          <t>94,32%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -11914,12 +11914,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>703759</t>
+          <t>704976</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>742373</t>
+          <t>742639</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -11929,12 +11929,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>89,42%</t>
+          <t>89,57%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>94,32%</t>
+          <t>94,36%</t>
         </is>
       </c>
     </row>
@@ -12074,12 +12074,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>2873</t>
+          <t>2851</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>10039</t>
+          <t>9798</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -12089,12 +12089,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>1,61%</t>
+          <t>1,6%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>5,62%</t>
+          <t>5,48%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -12109,12 +12109,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>13428</t>
+          <t>13672</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>25474</t>
+          <t>25426</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -12124,12 +12124,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>6,45%</t>
+          <t>6,57%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>12,25%</t>
+          <t>12,22%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -12144,12 +12144,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>18459</t>
+          <t>18053</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>31076</t>
+          <t>31408</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -12159,12 +12159,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>4,77%</t>
+          <t>4,67%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>8,03%</t>
+          <t>8,12%</t>
         </is>
       </c>
     </row>
@@ -12187,12 +12187,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>168703</t>
+          <t>168944</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>175869</t>
+          <t>175891</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -12202,12 +12202,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>94,38%</t>
+          <t>94,52%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>98,39%</t>
+          <t>98,4%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -12222,12 +12222,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>182559</t>
+          <t>182607</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>194605</t>
+          <t>194361</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -12237,12 +12237,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>87,75%</t>
+          <t>87,78%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>93,55%</t>
+          <t>93,43%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -12257,12 +12257,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>355699</t>
+          <t>355367</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>368316</t>
+          <t>368722</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -12272,12 +12272,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>91,97%</t>
+          <t>91,88%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>95,23%</t>
+          <t>95,33%</t>
         </is>
       </c>
     </row>
@@ -12417,12 +12417,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>8926</t>
+          <t>8946</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>21366</t>
+          <t>21133</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -12432,12 +12432,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>3,31%</t>
+          <t>3,32%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>7,92%</t>
+          <t>7,84%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -12452,12 +12452,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>13450</t>
+          <t>13133</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>25192</t>
+          <t>24284</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -12467,12 +12467,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>5,23%</t>
+          <t>5,11%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>9,8%</t>
+          <t>9,45%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -12487,12 +12487,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>25316</t>
+          <t>24532</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>41067</t>
+          <t>41076</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -12502,7 +12502,7 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>4,81%</t>
+          <t>4,66%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
@@ -12530,12 +12530,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>248270</t>
+          <t>248503</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>260710</t>
+          <t>260690</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -12545,12 +12545,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>92,08%</t>
+          <t>92,16%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>96,69%</t>
+          <t>96,68%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -12565,12 +12565,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>231864</t>
+          <t>232772</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>243606</t>
+          <t>243923</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -12580,12 +12580,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>90,2%</t>
+          <t>90,55%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>94,77%</t>
+          <t>94,89%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -12600,12 +12600,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>485625</t>
+          <t>485616</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>501376</t>
+          <t>502160</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -12620,7 +12620,7 @@
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>95,19%</t>
+          <t>95,34%</t>
         </is>
       </c>
     </row>
@@ -12760,12 +12760,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>36279</t>
+          <t>36585</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>67931</t>
+          <t>68259</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -12775,12 +12775,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>5,81%</t>
+          <t>5,86%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>10,88%</t>
+          <t>10,93%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -12795,12 +12795,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>43177</t>
+          <t>39556</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>118246</t>
+          <t>120369</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -12810,12 +12810,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>5,08%</t>
+          <t>4,66%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>13,92%</t>
+          <t>14,17%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -12830,12 +12830,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>82607</t>
+          <t>88071</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>167953</t>
+          <t>168947</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -12845,12 +12845,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>5,61%</t>
+          <t>5,98%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>11,4%</t>
+          <t>11,47%</t>
         </is>
       </c>
     </row>
@@ -12873,12 +12873,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>556348</t>
+          <t>556020</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>588000</t>
+          <t>587694</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -12888,12 +12888,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>89,12%</t>
+          <t>89,07%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>94,19%</t>
+          <t>94,14%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -12908,12 +12908,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>731019</t>
+          <t>728896</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>806088</t>
+          <t>809709</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -12923,12 +12923,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>86,08%</t>
+          <t>85,83%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>94,92%</t>
+          <t>95,34%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -12943,12 +12943,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>1305591</t>
+          <t>1304597</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>1390937</t>
+          <t>1385473</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -12958,12 +12958,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>88,6%</t>
+          <t>88,53%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>94,39%</t>
+          <t>94,02%</t>
         </is>
       </c>
     </row>
@@ -13103,12 +13103,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>15737</t>
+          <t>18262</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>60032</t>
+          <t>60301</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -13118,12 +13118,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>1,69%</t>
+          <t>1,97%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>6,46%</t>
+          <t>6,49%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -13138,12 +13138,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>94857</t>
+          <t>97168</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>131479</t>
+          <t>130631</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -13153,12 +13153,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>13,22%</t>
+          <t>13,54%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>18,32%</t>
+          <t>18,2%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -13173,12 +13173,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>94635</t>
+          <t>94856</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>186897</t>
+          <t>189787</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -13188,12 +13188,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>5,75%</t>
+          <t>5,76%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>11,35%</t>
+          <t>11,53%</t>
         </is>
       </c>
     </row>
@@ -13216,12 +13216,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>868688</t>
+          <t>868419</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>912983</t>
+          <t>910458</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -13231,12 +13231,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>93,54%</t>
+          <t>93,51%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>98,31%</t>
+          <t>98,03%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -13251,12 +13251,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>586252</t>
+          <t>587100</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>622874</t>
+          <t>620563</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -13266,12 +13266,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>81,68%</t>
+          <t>81,8%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>86,78%</t>
+          <t>86,46%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -13286,12 +13286,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>1459555</t>
+          <t>1456665</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>1551817</t>
+          <t>1551596</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -13301,12 +13301,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>88,65%</t>
+          <t>88,47%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>94,25%</t>
+          <t>94,24%</t>
         </is>
       </c>
     </row>
@@ -13446,12 +13446,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>143983</t>
+          <t>144095</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>218652</t>
+          <t>218060</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -13461,12 +13461,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>4,16%</t>
+          <t>4,17%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>6,32%</t>
+          <t>6,3%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -13481,12 +13481,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>297598</t>
+          <t>293952</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>405500</t>
+          <t>409591</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -13496,12 +13496,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>8,13%</t>
+          <t>8,03%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>11,08%</t>
+          <t>11,19%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -13516,12 +13516,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>477718</t>
+          <t>480796</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>608844</t>
+          <t>614848</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -13531,12 +13531,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>6,71%</t>
+          <t>6,75%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>8,55%</t>
+          <t>8,64%</t>
         </is>
       </c>
     </row>
@@ -13559,12 +13559,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>3239959</t>
+          <t>3240551</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>3314628</t>
+          <t>3314516</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -13574,12 +13574,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>93,68%</t>
+          <t>93,7%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>95,84%</t>
+          <t>95,83%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -13594,12 +13594,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>3254827</t>
+          <t>3250736</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>3362729</t>
+          <t>3366375</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -13609,12 +13609,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>88,92%</t>
+          <t>88,81%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>91,87%</t>
+          <t>91,97%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -13629,12 +13629,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>6510094</t>
+          <t>6504090</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>6641220</t>
+          <t>6638142</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -13644,12 +13644,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>91,45%</t>
+          <t>91,36%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>93,29%</t>
+          <t>93,25%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/P1002-Provincia-trans_orig.xlsx
+++ b/data/trans_orig/P1002-Provincia-trans_orig.xlsx
@@ -733,12 +733,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>12616</t>
+          <t>12586</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>29423</t>
+          <t>30041</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -748,12 +748,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>4,62%</t>
+          <t>4,61%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>10,78%</t>
+          <t>11,0%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>12968</t>
+          <t>12264</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>31419</t>
+          <t>30913</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -783,12 +783,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>4,97%</t>
+          <t>4,7%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>12,05%</t>
+          <t>11,85%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>29874</t>
+          <t>28722</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>54318</t>
+          <t>54596</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>5,6%</t>
+          <t>5,38%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>10,17%</t>
+          <t>10,23%</t>
         </is>
       </c>
     </row>
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>243587</t>
+          <t>242969</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>260394</t>
+          <t>260424</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -861,12 +861,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>89,22%</t>
+          <t>89,0%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>95,38%</t>
+          <t>95,39%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -881,12 +881,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>229419</t>
+          <t>229925</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>247870</t>
+          <t>248574</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -896,12 +896,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>87,95%</t>
+          <t>88,15%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>95,03%</t>
+          <t>95,3%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>479530</t>
+          <t>479252</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>503974</t>
+          <t>505126</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>89,83%</t>
+          <t>89,77%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>94,4%</t>
+          <t>94,62%</t>
         </is>
       </c>
     </row>
@@ -1076,12 +1076,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>25582</t>
+          <t>24410</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>49455</t>
+          <t>49039</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1091,12 +1091,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>5,19%</t>
+          <t>4,95%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>10,03%</t>
+          <t>9,95%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1111,12 +1111,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>59228</t>
+          <t>59831</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>92921</t>
+          <t>90633</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1126,12 +1126,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>11,75%</t>
+          <t>11,87%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>18,44%</t>
+          <t>17,98%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1146,12 +1146,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>91444</t>
+          <t>90796</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>130716</t>
+          <t>130057</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1161,12 +1161,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>9,17%</t>
+          <t>9,11%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>13,11%</t>
+          <t>13,04%</t>
         </is>
       </c>
     </row>
@@ -1189,12 +1189,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>443620</t>
+          <t>444036</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>467493</t>
+          <t>468665</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1204,12 +1204,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>89,97%</t>
+          <t>90,05%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>94,81%</t>
+          <t>95,05%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1224,12 +1224,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>411028</t>
+          <t>413316</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>444721</t>
+          <t>444118</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1239,12 +1239,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>81,56%</t>
+          <t>82,02%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>88,25%</t>
+          <t>88,13%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>866308</t>
+          <t>866967</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>905580</t>
+          <t>906228</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,12 +1274,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>86,89%</t>
+          <t>86,96%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>90,83%</t>
+          <t>90,89%</t>
         </is>
       </c>
     </row>
@@ -1419,12 +1419,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>942</t>
+          <t>941</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>11467</t>
+          <t>11258</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1439,7 +1439,7 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>3,6%</t>
+          <t>3,53%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1454,12 +1454,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>6449</t>
+          <t>6212</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>20927</t>
+          <t>19573</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1469,12 +1469,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>1,92%</t>
+          <t>1,85%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>6,24%</t>
+          <t>5,84%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1489,12 +1489,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>8931</t>
+          <t>8407</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>25374</t>
+          <t>25204</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1504,12 +1504,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>1,37%</t>
+          <t>1,29%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>3,88%</t>
+          <t>3,85%</t>
         </is>
       </c>
     </row>
@@ -1532,12 +1532,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>307379</t>
+          <t>307588</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>317904</t>
+          <t>317905</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1547,7 +1547,7 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>96,4%</t>
+          <t>96,47%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
@@ -1567,12 +1567,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>314485</t>
+          <t>315839</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>328963</t>
+          <t>329200</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1582,12 +1582,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>93,76%</t>
+          <t>94,16%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>98,08%</t>
+          <t>98,15%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1602,12 +1602,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>628884</t>
+          <t>629054</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>645327</t>
+          <t>645851</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1617,12 +1617,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>96,12%</t>
+          <t>96,15%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>98,63%</t>
+          <t>98,71%</t>
         </is>
       </c>
     </row>
@@ -1762,12 +1762,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>2634</t>
+          <t>2466</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>12553</t>
+          <t>12797</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1777,12 +1777,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>0,73%</t>
+          <t>0,69%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>3,5%</t>
+          <t>3,57%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1797,12 +1797,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>16735</t>
+          <t>16933</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>35791</t>
+          <t>37103</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1812,12 +1812,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>4,51%</t>
+          <t>4,56%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>9,64%</t>
+          <t>9,99%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1832,12 +1832,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>21335</t>
+          <t>21383</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>43397</t>
+          <t>45113</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1847,12 +1847,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>2,92%</t>
+          <t>2,93%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>5,94%</t>
+          <t>6,18%</t>
         </is>
       </c>
     </row>
@@ -1875,12 +1875,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>346118</t>
+          <t>345874</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>356037</t>
+          <t>356205</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1890,12 +1890,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>96,5%</t>
+          <t>96,43%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>99,27%</t>
+          <t>99,31%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1910,12 +1910,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>335665</t>
+          <t>334353</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>354721</t>
+          <t>354523</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1925,12 +1925,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>90,36%</t>
+          <t>90,01%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>95,49%</t>
+          <t>95,44%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>686730</t>
+          <t>685014</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>708792</t>
+          <t>708744</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1960,12 +1960,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>94,06%</t>
+          <t>93,82%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>97,08%</t>
+          <t>97,07%</t>
         </is>
       </c>
     </row>
@@ -2105,12 +2105,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>7533</t>
+          <t>7359</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>20335</t>
+          <t>19391</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2120,12 +2120,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>3,71%</t>
+          <t>3,62%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>10,0%</t>
+          <t>9,54%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2140,12 +2140,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>6117</t>
+          <t>6991</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>19728</t>
+          <t>20534</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2155,12 +2155,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>2,95%</t>
+          <t>3,37%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>9,5%</t>
+          <t>9,89%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2175,12 +2175,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>16513</t>
+          <t>17076</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>35513</t>
+          <t>35822</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2190,12 +2190,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>4,02%</t>
+          <t>4,15%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>8,64%</t>
+          <t>8,72%</t>
         </is>
       </c>
     </row>
@@ -2218,12 +2218,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>182973</t>
+          <t>183917</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>195775</t>
+          <t>195949</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2233,12 +2233,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>90,0%</t>
+          <t>90,46%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>96,29%</t>
+          <t>96,38%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2253,12 +2253,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>187940</t>
+          <t>187134</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>201551</t>
+          <t>200677</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2268,12 +2268,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>90,5%</t>
+          <t>90,11%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>97,05%</t>
+          <t>96,63%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2288,12 +2288,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>375463</t>
+          <t>375154</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>394463</t>
+          <t>393900</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2303,12 +2303,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>91,36%</t>
+          <t>91,28%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>95,98%</t>
+          <t>95,85%</t>
         </is>
       </c>
     </row>
@@ -2448,12 +2448,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>878</t>
+          <t>936</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>8586</t>
+          <t>9132</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2463,12 +2463,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>0,32%</t>
+          <t>0,35%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>3,17%</t>
+          <t>3,37%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2483,12 +2483,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>5496</t>
+          <t>5378</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>18712</t>
+          <t>18844</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2498,12 +2498,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>1,98%</t>
+          <t>1,93%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>6,73%</t>
+          <t>6,78%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2518,12 +2518,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>7554</t>
+          <t>8508</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>22376</t>
+          <t>23112</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2533,12 +2533,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>1,38%</t>
+          <t>1,55%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>4,08%</t>
+          <t>4,21%</t>
         </is>
       </c>
     </row>
@@ -2561,12 +2561,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>262225</t>
+          <t>261679</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>269933</t>
+          <t>269875</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2576,12 +2576,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>96,83%</t>
+          <t>96,63%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>99,68%</t>
+          <t>99,65%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2596,12 +2596,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>259432</t>
+          <t>259300</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>272648</t>
+          <t>272766</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2611,12 +2611,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>93,27%</t>
+          <t>93,22%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>98,02%</t>
+          <t>98,07%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2631,12 +2631,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>526579</t>
+          <t>525843</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>541401</t>
+          <t>540447</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2646,12 +2646,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>95,92%</t>
+          <t>95,79%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>98,62%</t>
+          <t>98,45%</t>
         </is>
       </c>
     </row>
@@ -2791,12 +2791,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>21442</t>
+          <t>21653</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>44437</t>
+          <t>44019</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2806,12 +2806,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>3,49%</t>
+          <t>3,52%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>7,23%</t>
+          <t>7,16%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2826,12 +2826,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>47493</t>
+          <t>46874</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>75575</t>
+          <t>75350</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2841,12 +2841,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>7,44%</t>
+          <t>7,34%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>11,84%</t>
+          <t>11,81%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2861,12 +2861,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>74805</t>
+          <t>75997</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>110299</t>
+          <t>111956</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2876,12 +2876,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>5,97%</t>
+          <t>6,06%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>8,8%</t>
+          <t>8,93%</t>
         </is>
       </c>
     </row>
@@ -2904,12 +2904,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>570590</t>
+          <t>571008</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>593585</t>
+          <t>593374</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2919,12 +2919,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>92,77%</t>
+          <t>92,84%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>96,51%</t>
+          <t>96,48%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2939,12 +2939,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>562644</t>
+          <t>562869</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>590726</t>
+          <t>591345</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2954,12 +2954,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>88,16%</t>
+          <t>88,19%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>92,56%</t>
+          <t>92,66%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2974,12 +2974,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>1142947</t>
+          <t>1141290</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>1178441</t>
+          <t>1177249</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2989,12 +2989,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>91,2%</t>
+          <t>91,07%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>94,03%</t>
+          <t>93,94%</t>
         </is>
       </c>
     </row>
@@ -3134,12 +3134,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>44095</t>
+          <t>43181</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>73711</t>
+          <t>72510</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3149,12 +3149,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>5,93%</t>
+          <t>5,81%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>9,91%</t>
+          <t>9,75%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3169,12 +3169,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>56905</t>
+          <t>57154</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>88992</t>
+          <t>89297</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3184,12 +3184,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>7,26%</t>
+          <t>7,29%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>11,36%</t>
+          <t>11,4%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3204,12 +3204,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>110203</t>
+          <t>107186</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>155330</t>
+          <t>151029</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3219,12 +3219,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>7,22%</t>
+          <t>7,02%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>10,17%</t>
+          <t>9,89%</t>
         </is>
       </c>
     </row>
@@ -3247,12 +3247,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>670084</t>
+          <t>671285</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>699700</t>
+          <t>700614</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3262,12 +3262,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>90,09%</t>
+          <t>90,25%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>94,07%</t>
+          <t>94,19%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3282,12 +3282,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>694519</t>
+          <t>694214</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>726606</t>
+          <t>726357</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3297,12 +3297,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>88,64%</t>
+          <t>88,6%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>92,74%</t>
+          <t>92,71%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3317,12 +3317,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>1371976</t>
+          <t>1376277</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>1417103</t>
+          <t>1420120</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3332,12 +3332,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>89,83%</t>
+          <t>90,11%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>92,78%</t>
+          <t>92,98%</t>
         </is>
       </c>
     </row>
@@ -3477,12 +3477,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>146756</t>
+          <t>148464</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>198797</t>
+          <t>198912</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -3492,7 +3492,7 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>4,48%</t>
+          <t>4,53%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
@@ -3512,12 +3512,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>254321</t>
+          <t>256407</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>320284</t>
+          <t>320052</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -3527,12 +3527,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>7,53%</t>
+          <t>7,59%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>9,48%</t>
+          <t>9,47%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3547,12 +3547,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>416760</t>
+          <t>417963</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>498152</t>
+          <t>503940</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -3562,12 +3562,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>6,26%</t>
+          <t>6,28%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>7,48%</t>
+          <t>7,57%</t>
         </is>
       </c>
     </row>
@@ -3590,12 +3590,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>3077746</t>
+          <t>3077631</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>3129787</t>
+          <t>3128079</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -3610,7 +3610,7 @@
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>95,52%</t>
+          <t>95,47%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -3625,12 +3625,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>3058913</t>
+          <t>3059145</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>3124876</t>
+          <t>3122790</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -3640,12 +3640,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>90,52%</t>
+          <t>90,53%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>92,47%</t>
+          <t>92,41%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3660,12 +3660,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>6157589</t>
+          <t>6151801</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>6238981</t>
+          <t>6237778</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -3675,12 +3675,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>92,52%</t>
+          <t>92,43%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>93,74%</t>
+          <t>93,72%</t>
         </is>
       </c>
     </row>
@@ -4056,12 +4056,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>17369</t>
+          <t>18058</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>37268</t>
+          <t>37968</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -4071,12 +4071,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>5,89%</t>
+          <t>6,13%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>12,64%</t>
+          <t>12,88%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -4091,12 +4091,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>43907</t>
+          <t>43246</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>71759</t>
+          <t>72125</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -4106,12 +4106,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>15,29%</t>
+          <t>15,06%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>24,98%</t>
+          <t>25,11%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -4126,12 +4126,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>67437</t>
+          <t>66859</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>102271</t>
+          <t>104995</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -4141,12 +4141,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>11,59%</t>
+          <t>11,49%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>17,57%</t>
+          <t>18,04%</t>
         </is>
       </c>
     </row>
@@ -4169,12 +4169,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>257470</t>
+          <t>256770</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>277369</t>
+          <t>276680</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -4184,12 +4184,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>87,36%</t>
+          <t>87,12%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>94,11%</t>
+          <t>93,87%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -4204,12 +4204,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>215486</t>
+          <t>215120</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>243338</t>
+          <t>243999</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -4219,12 +4219,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>75,02%</t>
+          <t>74,89%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>84,71%</t>
+          <t>84,94%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -4239,12 +4239,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>479712</t>
+          <t>476988</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>514546</t>
+          <t>515124</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -4254,12 +4254,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>82,43%</t>
+          <t>81,96%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>88,41%</t>
+          <t>88,51%</t>
         </is>
       </c>
     </row>
@@ -4399,12 +4399,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>27286</t>
+          <t>28087</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>54452</t>
+          <t>54286</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4414,12 +4414,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>5,4%</t>
+          <t>5,56%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>10,77%</t>
+          <t>10,74%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -4434,12 +4434,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>61071</t>
+          <t>62180</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>95859</t>
+          <t>94726</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -4449,12 +4449,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>11,68%</t>
+          <t>11,9%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>18,34%</t>
+          <t>18,12%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -4469,12 +4469,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>98266</t>
+          <t>97403</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>140918</t>
+          <t>140137</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -4484,12 +4484,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>9,56%</t>
+          <t>9,47%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>13,7%</t>
+          <t>13,63%</t>
         </is>
       </c>
     </row>
@@ -4512,12 +4512,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>451075</t>
+          <t>451241</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>478241</t>
+          <t>477440</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -4527,12 +4527,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>89,23%</t>
+          <t>89,26%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>94,6%</t>
+          <t>94,44%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -4547,12 +4547,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>426851</t>
+          <t>427984</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>461639</t>
+          <t>460530</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -4562,12 +4562,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>81,66%</t>
+          <t>81,88%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>88,32%</t>
+          <t>88,1%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -4582,12 +4582,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>887319</t>
+          <t>888100</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>929971</t>
+          <t>930834</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -4597,12 +4597,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>86,3%</t>
+          <t>86,37%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>90,44%</t>
+          <t>90,53%</t>
         </is>
       </c>
     </row>
@@ -4742,12 +4742,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>11164</t>
+          <t>10598</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>28847</t>
+          <t>27861</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -4757,12 +4757,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>3,45%</t>
+          <t>3,27%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>8,9%</t>
+          <t>8,6%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -4777,12 +4777,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>26960</t>
+          <t>26614</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>51268</t>
+          <t>50724</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -4792,12 +4792,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>7,91%</t>
+          <t>7,8%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>15,03%</t>
+          <t>14,87%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -4812,12 +4812,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>42075</t>
+          <t>41818</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>72713</t>
+          <t>71249</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4827,12 +4827,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>6,33%</t>
+          <t>6,29%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>10,93%</t>
+          <t>10,71%</t>
         </is>
       </c>
     </row>
@@ -4855,12 +4855,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>295199</t>
+          <t>296185</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>312882</t>
+          <t>313448</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -4870,12 +4870,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>91,1%</t>
+          <t>91,4%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>96,55%</t>
+          <t>96,73%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -4890,12 +4890,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>289752</t>
+          <t>290296</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>314060</t>
+          <t>314406</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -4905,12 +4905,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>84,97%</t>
+          <t>85,13%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>92,09%</t>
+          <t>92,2%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -4925,12 +4925,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>592353</t>
+          <t>593817</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>622991</t>
+          <t>623248</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -4940,12 +4940,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>89,07%</t>
+          <t>89,29%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>93,67%</t>
+          <t>93,71%</t>
         </is>
       </c>
     </row>
@@ -5085,12 +5085,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>14798</t>
+          <t>14636</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>33946</t>
+          <t>33258</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -5100,12 +5100,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>3,96%</t>
+          <t>3,91%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>9,08%</t>
+          <t>8,89%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -5120,12 +5120,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>65771</t>
+          <t>64786</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>96924</t>
+          <t>96781</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -5135,12 +5135,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>16,91%</t>
+          <t>16,66%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>24,92%</t>
+          <t>24,88%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5155,12 +5155,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>87187</t>
+          <t>86183</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>124140</t>
+          <t>124169</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5170,12 +5170,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>11,43%</t>
+          <t>11,3%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>16,27%</t>
+          <t>16,28%</t>
         </is>
       </c>
     </row>
@@ -5198,12 +5198,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>340036</t>
+          <t>340724</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>359184</t>
+          <t>359346</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -5213,12 +5213,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>90,92%</t>
+          <t>91,11%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>96,04%</t>
+          <t>96,09%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -5233,12 +5233,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>292027</t>
+          <t>292170</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>323180</t>
+          <t>324165</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -5248,12 +5248,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>75,08%</t>
+          <t>75,12%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>83,09%</t>
+          <t>83,34%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -5268,12 +5268,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>638793</t>
+          <t>638764</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>675746</t>
+          <t>676750</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -5283,12 +5283,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>83,73%</t>
+          <t>83,72%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>88,57%</t>
+          <t>88,7%</t>
         </is>
       </c>
     </row>
@@ -5428,12 +5428,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>4324</t>
+          <t>4319</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>16662</t>
+          <t>17039</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -5448,7 +5448,7 @@
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>7,84%</t>
+          <t>8,01%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -5463,12 +5463,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>27652</t>
+          <t>27426</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>50417</t>
+          <t>50845</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -5478,12 +5478,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>12,59%</t>
+          <t>12,49%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>22,96%</t>
+          <t>23,15%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -5498,12 +5498,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>35219</t>
+          <t>35116</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>60456</t>
+          <t>62256</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -5513,12 +5513,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>8,15%</t>
+          <t>8,12%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>13,99%</t>
+          <t>14,4%</t>
         </is>
       </c>
     </row>
@@ -5541,12 +5541,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>195956</t>
+          <t>195579</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>208294</t>
+          <t>208299</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -5556,7 +5556,7 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>92,16%</t>
+          <t>91,99%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
@@ -5576,12 +5576,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>169174</t>
+          <t>168746</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>191939</t>
+          <t>192165</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -5591,12 +5591,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>77,04%</t>
+          <t>76,85%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>87,41%</t>
+          <t>87,51%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -5611,12 +5611,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>371753</t>
+          <t>369953</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>396990</t>
+          <t>397093</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -5626,12 +5626,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>86,01%</t>
+          <t>85,6%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>91,85%</t>
+          <t>91,88%</t>
         </is>
       </c>
     </row>
@@ -5771,12 +5771,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>11503</t>
+          <t>12047</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>29105</t>
+          <t>29435</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -5786,12 +5786,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>4,21%</t>
+          <t>4,41%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>10,66%</t>
+          <t>10,78%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -5806,12 +5806,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>20668</t>
+          <t>20561</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>40424</t>
+          <t>39670</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -5821,12 +5821,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>7,38%</t>
+          <t>7,34%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>14,44%</t>
+          <t>14,17%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -5841,12 +5841,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>38232</t>
+          <t>36522</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>62162</t>
+          <t>63113</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -5856,12 +5856,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>6,91%</t>
+          <t>6,6%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>11,24%</t>
+          <t>11,41%</t>
         </is>
       </c>
     </row>
@@ -5884,12 +5884,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>243822</t>
+          <t>243492</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>261424</t>
+          <t>260880</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -5899,12 +5899,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>89,34%</t>
+          <t>89,22%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>95,79%</t>
+          <t>95,59%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -5919,12 +5919,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>239607</t>
+          <t>240361</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>259363</t>
+          <t>259470</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -5934,12 +5934,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>85,56%</t>
+          <t>85,83%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>92,62%</t>
+          <t>92,66%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -5954,12 +5954,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>490796</t>
+          <t>489845</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>514726</t>
+          <t>516436</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -5969,12 +5969,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>88,76%</t>
+          <t>88,59%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>93,09%</t>
+          <t>93,4%</t>
         </is>
       </c>
     </row>
@@ -6114,12 +6114,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>18117</t>
+          <t>17925</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>40302</t>
+          <t>41683</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -6129,12 +6129,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>2,73%</t>
+          <t>2,7%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>6,08%</t>
+          <t>6,29%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -6149,12 +6149,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>37850</t>
+          <t>39110</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>66858</t>
+          <t>68848</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -6164,12 +6164,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>5,46%</t>
+          <t>5,64%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>9,65%</t>
+          <t>9,94%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -6184,12 +6184,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>63301</t>
+          <t>63129</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>99140</t>
+          <t>100941</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -6199,12 +6199,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>4,67%</t>
+          <t>4,66%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>7,31%</t>
+          <t>7,45%</t>
         </is>
       </c>
     </row>
@@ -6227,12 +6227,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>622486</t>
+          <t>621105</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>644671</t>
+          <t>644863</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -6242,12 +6242,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>93,92%</t>
+          <t>93,71%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>97,27%</t>
+          <t>97,3%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -6262,12 +6262,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>626050</t>
+          <t>624060</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>655058</t>
+          <t>653798</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -6277,12 +6277,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>90,35%</t>
+          <t>90,06%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>94,54%</t>
+          <t>94,36%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -6297,12 +6297,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>1256556</t>
+          <t>1254755</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>1292395</t>
+          <t>1292567</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -6312,12 +6312,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>92,69%</t>
+          <t>92,55%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>95,33%</t>
+          <t>95,34%</t>
         </is>
       </c>
     </row>
@@ -6457,12 +6457,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>50133</t>
+          <t>51168</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>85490</t>
+          <t>84870</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -6472,12 +6472,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>6,44%</t>
+          <t>6,58%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>10,99%</t>
+          <t>10,91%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -6492,12 +6492,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>104440</t>
+          <t>105227</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>146397</t>
+          <t>146295</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -6507,12 +6507,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>12,68%</t>
+          <t>12,77%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>17,77%</t>
+          <t>17,76%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -6527,12 +6527,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>166998</t>
+          <t>165152</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>220993</t>
+          <t>220846</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -6542,7 +6542,7 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>10,42%</t>
+          <t>10,31%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
@@ -6570,12 +6570,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>692671</t>
+          <t>693291</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>728028</t>
+          <t>726993</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -6585,12 +6585,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>89,01%</t>
+          <t>89,09%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>93,56%</t>
+          <t>93,42%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -6605,12 +6605,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>677456</t>
+          <t>677558</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>719413</t>
+          <t>718626</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -6620,12 +6620,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>82,23%</t>
+          <t>82,24%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>87,32%</t>
+          <t>87,23%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -6640,12 +6640,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>1381021</t>
+          <t>1381168</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>1435016</t>
+          <t>1436862</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -6660,7 +6660,7 @@
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>89,58%</t>
+          <t>89,69%</t>
         </is>
       </c>
     </row>
@@ -6800,12 +6800,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>200223</t>
+          <t>203429</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>262762</t>
+          <t>264601</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -6815,12 +6815,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>5,85%</t>
+          <t>5,94%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>7,67%</t>
+          <t>7,73%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -6835,12 +6835,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>458486</t>
+          <t>458375</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>543955</t>
+          <t>538013</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -6855,7 +6855,7 @@
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>15,3%</t>
+          <t>15,13%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -6870,12 +6870,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>676277</t>
+          <t>677517</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>777108</t>
+          <t>780673</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -6885,12 +6885,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>9,69%</t>
+          <t>9,71%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>11,13%</t>
+          <t>11,18%</t>
         </is>
       </c>
     </row>
@@ -6913,12 +6913,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>3162026</t>
+          <t>3160187</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>3224565</t>
+          <t>3221359</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -6928,12 +6928,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>92,33%</t>
+          <t>92,27%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>94,15%</t>
+          <t>94,06%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -6948,12 +6948,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>3012354</t>
+          <t>3018296</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>3097823</t>
+          <t>3097934</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -6963,7 +6963,7 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>84,7%</t>
+          <t>84,87%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
@@ -6983,12 +6983,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>6203989</t>
+          <t>6200424</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>6304820</t>
+          <t>6303580</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -6998,12 +6998,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>88,87%</t>
+          <t>88,82%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>90,31%</t>
+          <t>90,29%</t>
         </is>
       </c>
     </row>
@@ -7379,12 +7379,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>18116</t>
+          <t>17936</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>39630</t>
+          <t>38426</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -7394,12 +7394,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>6,17%</t>
+          <t>6,11%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>13,49%</t>
+          <t>13,08%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -7414,12 +7414,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>44206</t>
+          <t>44554</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>72580</t>
+          <t>70855</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -7429,12 +7429,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>15,31%</t>
+          <t>15,43%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>25,14%</t>
+          <t>24,54%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -7449,12 +7449,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>66655</t>
+          <t>68285</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>101987</t>
+          <t>101383</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -7464,12 +7464,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>11,44%</t>
+          <t>11,72%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>17,51%</t>
+          <t>17,41%</t>
         </is>
       </c>
     </row>
@@ -7492,12 +7492,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>254131</t>
+          <t>255335</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>275645</t>
+          <t>275825</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -7507,12 +7507,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>86,51%</t>
+          <t>86,92%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>93,83%</t>
+          <t>93,89%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -7527,12 +7527,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>216123</t>
+          <t>217848</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>244497</t>
+          <t>244149</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -7542,12 +7542,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>74,86%</t>
+          <t>75,46%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>84,69%</t>
+          <t>84,57%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -7562,12 +7562,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>480477</t>
+          <t>481081</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>515809</t>
+          <t>514179</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -7577,12 +7577,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>82,49%</t>
+          <t>82,59%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>88,56%</t>
+          <t>88,28%</t>
         </is>
       </c>
     </row>
@@ -7722,12 +7722,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>7149</t>
+          <t>7276</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>21726</t>
+          <t>21770</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -7737,12 +7737,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>1,42%</t>
+          <t>1,45%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>4,32%</t>
+          <t>4,33%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -7757,12 +7757,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>31031</t>
+          <t>29362</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>56775</t>
+          <t>55327</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -7772,12 +7772,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>5,93%</t>
+          <t>5,61%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>10,85%</t>
+          <t>10,58%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -7792,12 +7792,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>41586</t>
+          <t>42153</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>72355</t>
+          <t>71794</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -7807,12 +7807,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>4,05%</t>
+          <t>4,11%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>7,05%</t>
+          <t>7,0%</t>
         </is>
       </c>
     </row>
@@ -7835,12 +7835,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>480849</t>
+          <t>480805</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>495426</t>
+          <t>495299</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -7850,12 +7850,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>95,68%</t>
+          <t>95,67%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>98,58%</t>
+          <t>98,55%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -7870,12 +7870,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>466309</t>
+          <t>467757</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>492053</t>
+          <t>493722</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -7885,12 +7885,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>89,15%</t>
+          <t>89,42%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>94,07%</t>
+          <t>94,39%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -7905,12 +7905,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>953304</t>
+          <t>953865</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>984073</t>
+          <t>983506</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -7920,12 +7920,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>92,95%</t>
+          <t>93,0%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>95,95%</t>
+          <t>95,89%</t>
         </is>
       </c>
     </row>
@@ -8065,12 +8065,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>3083</t>
+          <t>2753</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>13826</t>
+          <t>13654</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -8080,12 +8080,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>0,97%</t>
+          <t>0,86%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>4,34%</t>
+          <t>4,29%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -8100,12 +8100,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>10573</t>
+          <t>9554</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>27401</t>
+          <t>27614</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -8115,12 +8115,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>3,14%</t>
+          <t>2,84%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>8,15%</t>
+          <t>8,21%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -8135,12 +8135,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>14780</t>
+          <t>15644</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>34206</t>
+          <t>36196</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -8150,12 +8150,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>2,26%</t>
+          <t>2,39%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>5,22%</t>
+          <t>5,53%</t>
         </is>
       </c>
     </row>
@@ -8178,12 +8178,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>304739</t>
+          <t>304911</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>315482</t>
+          <t>315812</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -8193,12 +8193,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>95,66%</t>
+          <t>95,71%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>99,03%</t>
+          <t>99,14%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -8213,12 +8213,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>308908</t>
+          <t>308695</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>325736</t>
+          <t>326755</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -8228,12 +8228,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>91,85%</t>
+          <t>91,79%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>96,86%</t>
+          <t>97,16%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -8248,12 +8248,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>620668</t>
+          <t>618678</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>640094</t>
+          <t>639230</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -8263,12 +8263,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>94,78%</t>
+          <t>94,47%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>97,74%</t>
+          <t>97,61%</t>
         </is>
       </c>
     </row>
@@ -8408,12 +8408,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>21859</t>
+          <t>22468</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>43904</t>
+          <t>43147</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -8423,12 +8423,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>5,91%</t>
+          <t>6,07%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>11,87%</t>
+          <t>11,66%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -8443,12 +8443,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>57593</t>
+          <t>58887</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>90549</t>
+          <t>90193</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -8458,12 +8458,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>14,87%</t>
+          <t>15,21%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>23,38%</t>
+          <t>23,29%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -8478,12 +8478,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>84952</t>
+          <t>87161</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>126756</t>
+          <t>124616</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -8493,12 +8493,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>11,22%</t>
+          <t>11,51%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>16,74%</t>
+          <t>16,46%</t>
         </is>
       </c>
     </row>
@@ -8521,12 +8521,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>326060</t>
+          <t>326817</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>348105</t>
+          <t>347496</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -8536,12 +8536,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>88,13%</t>
+          <t>88,34%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>94,09%</t>
+          <t>93,93%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -8556,12 +8556,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>296734</t>
+          <t>297090</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>329690</t>
+          <t>328396</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -8571,12 +8571,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>76,62%</t>
+          <t>76,71%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>85,13%</t>
+          <t>84,79%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -8591,12 +8591,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>630491</t>
+          <t>632631</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>672295</t>
+          <t>670086</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -8606,12 +8606,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>83,26%</t>
+          <t>83,54%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>88,78%</t>
+          <t>88,49%</t>
         </is>
       </c>
     </row>
@@ -8751,12 +8751,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>4026</t>
+          <t>3982</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>15814</t>
+          <t>15495</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -8766,12 +8766,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>1,91%</t>
+          <t>1,89%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>7,49%</t>
+          <t>7,34%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -8786,12 +8786,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>11027</t>
+          <t>10654</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>27743</t>
+          <t>25549</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -8801,12 +8801,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>5,04%</t>
+          <t>4,87%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>12,69%</t>
+          <t>11,69%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -8821,12 +8821,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>17660</t>
+          <t>17194</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>38936</t>
+          <t>37092</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -8836,12 +8836,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>4,11%</t>
+          <t>4,0%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>9,06%</t>
+          <t>8,63%</t>
         </is>
       </c>
     </row>
@@ -8864,12 +8864,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>195407</t>
+          <t>195726</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>207195</t>
+          <t>207239</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -8879,12 +8879,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>92,51%</t>
+          <t>92,66%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>98,09%</t>
+          <t>98,11%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -8899,12 +8899,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>190844</t>
+          <t>193038</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>207560</t>
+          <t>207933</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -8914,12 +8914,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>87,31%</t>
+          <t>88,31%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>94,96%</t>
+          <t>95,13%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -8934,12 +8934,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>390872</t>
+          <t>392716</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>412148</t>
+          <t>412614</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -8949,12 +8949,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>90,94%</t>
+          <t>91,37%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>95,89%</t>
+          <t>96,0%</t>
         </is>
       </c>
     </row>
@@ -9094,12 +9094,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>13542</t>
+          <t>13530</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>31765</t>
+          <t>31868</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -9109,12 +9109,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>5,15%</t>
+          <t>5,14%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>12,07%</t>
+          <t>12,11%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -9129,12 +9129,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>25260</t>
+          <t>22724</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>48064</t>
+          <t>46617</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -9144,12 +9144,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>9,25%</t>
+          <t>8,32%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>17,6%</t>
+          <t>17,07%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -9164,12 +9164,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>40532</t>
+          <t>42074</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>69692</t>
+          <t>71683</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -9179,12 +9179,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>7,56%</t>
+          <t>7,85%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>13,0%</t>
+          <t>13,37%</t>
         </is>
       </c>
     </row>
@@ -9207,12 +9207,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>231358</t>
+          <t>231255</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>249581</t>
+          <t>249593</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -9222,12 +9222,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>87,93%</t>
+          <t>87,89%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>94,85%</t>
+          <t>94,86%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -9242,12 +9242,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>225051</t>
+          <t>226498</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>247855</t>
+          <t>250391</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -9257,12 +9257,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>82,4%</t>
+          <t>82,93%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>90,75%</t>
+          <t>91,68%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -9277,12 +9277,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>466546</t>
+          <t>464555</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>495706</t>
+          <t>494164</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -9292,12 +9292,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>87,0%</t>
+          <t>86,63%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>92,44%</t>
+          <t>92,15%</t>
         </is>
       </c>
     </row>
@@ -9437,12 +9437,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>28688</t>
+          <t>27494</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>55172</t>
+          <t>54904</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -9452,12 +9452,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>4,37%</t>
+          <t>4,19%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>8,4%</t>
+          <t>8,36%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -9472,12 +9472,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>64632</t>
+          <t>63732</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>100284</t>
+          <t>100007</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -9487,12 +9487,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>9,35%</t>
+          <t>9,22%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>14,51%</t>
+          <t>14,47%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -9507,12 +9507,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>101439</t>
+          <t>100493</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>145134</t>
+          <t>145028</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -9522,12 +9522,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>7,53%</t>
+          <t>7,46%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>10,77%</t>
+          <t>10,76%</t>
         </is>
       </c>
     </row>
@@ -9550,12 +9550,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>601386</t>
+          <t>601654</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>627870</t>
+          <t>629064</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -9565,12 +9565,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>91,6%</t>
+          <t>91,64%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>95,63%</t>
+          <t>95,81%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -9585,12 +9585,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>591010</t>
+          <t>591287</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>626662</t>
+          <t>627562</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -9600,12 +9600,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>85,49%</t>
+          <t>85,53%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>90,65%</t>
+          <t>90,78%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -9620,12 +9620,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>1202718</t>
+          <t>1202824</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>1246413</t>
+          <t>1247359</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -9635,12 +9635,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>89,23%</t>
+          <t>89,24%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>92,47%</t>
+          <t>92,54%</t>
         </is>
       </c>
     </row>
@@ -9780,12 +9780,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>22650</t>
+          <t>23072</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>44029</t>
+          <t>44489</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -9795,12 +9795,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>2,91%</t>
+          <t>2,96%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>5,66%</t>
+          <t>5,71%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -9815,12 +9815,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>42652</t>
+          <t>42794</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>73945</t>
+          <t>74238</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -9830,12 +9830,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>5,16%</t>
+          <t>5,18%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>8,95%</t>
+          <t>8,99%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -9850,12 +9850,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>71772</t>
+          <t>72592</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>110584</t>
+          <t>108413</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -9865,12 +9865,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>4,47%</t>
+          <t>4,52%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>6,89%</t>
+          <t>6,76%</t>
         </is>
       </c>
     </row>
@@ -9893,12 +9893,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>734554</t>
+          <t>734094</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>755933</t>
+          <t>755511</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -9908,12 +9908,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>94,34%</t>
+          <t>94,29%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>97,09%</t>
+          <t>97,04%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -9928,12 +9928,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>752222</t>
+          <t>751929</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>783515</t>
+          <t>783373</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -9943,12 +9943,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>91,05%</t>
+          <t>91,01%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>94,84%</t>
+          <t>94,82%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -9963,12 +9963,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>1494166</t>
+          <t>1496337</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>1532978</t>
+          <t>1532158</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -9978,12 +9978,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>93,11%</t>
+          <t>93,24%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>95,53%</t>
+          <t>95,48%</t>
         </is>
       </c>
     </row>
@@ -10123,12 +10123,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>155036</t>
+          <t>158177</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>210026</t>
+          <t>210644</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -10138,12 +10138,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>4,57%</t>
+          <t>4,66%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>6,19%</t>
+          <t>6,21%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -10158,12 +10158,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>342362</t>
+          <t>337941</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>420308</t>
+          <t>419802</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -10173,12 +10173,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>9,66%</t>
+          <t>9,53%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>11,86%</t>
+          <t>11,84%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -10193,12 +10193,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>512495</t>
+          <t>514784</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>607279</t>
+          <t>607076</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -10208,7 +10208,7 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>7,39%</t>
+          <t>7,42%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
@@ -10236,12 +10236,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>3184324</t>
+          <t>3183706</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>3239314</t>
+          <t>3236173</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -10251,12 +10251,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>93,81%</t>
+          <t>93,79%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>95,43%</t>
+          <t>95,34%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -10271,12 +10271,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>3124234</t>
+          <t>3124740</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>3202180</t>
+          <t>3206601</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -10286,12 +10286,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>88,14%</t>
+          <t>88,16%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>90,34%</t>
+          <t>90,47%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -10306,12 +10306,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>6331613</t>
+          <t>6331816</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>6426397</t>
+          <t>6424108</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -10326,7 +10326,7 @@
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>92,61%</t>
+          <t>92,58%</t>
         </is>
       </c>
     </row>
@@ -10697,32 +10697,32 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>6276</t>
+          <t>5508</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>2281</t>
+          <t>1783</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>14060</t>
+          <t>10794</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>2,01%</t>
+          <t>1,73%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>0,73%</t>
+          <t>0,56%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>4,51%</t>
+          <t>3,39%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -10732,32 +10732,32 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>8638</t>
+          <t>9040</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>5185</t>
+          <t>5264</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>15144</t>
+          <t>14611</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>2,98%</t>
+          <t>2,86%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>1,79%</t>
+          <t>1,67%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>5,23%</t>
+          <t>4,62%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -10767,32 +10767,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>14914</t>
+          <t>14548</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>9317</t>
+          <t>9231</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>23415</t>
+          <t>20902</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>2,48%</t>
+          <t>2,29%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>1,55%</t>
+          <t>1,45%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>3,9%</t>
+          <t>3,29%</t>
         </is>
       </c>
     </row>
@@ -10810,32 +10810,32 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>305167</t>
+          <t>313337</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>297383</t>
+          <t>308051</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>309162</t>
+          <t>317062</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>97,99%</t>
+          <t>98,27%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>95,49%</t>
+          <t>96,61%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>99,27%</t>
+          <t>99,44%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -10845,32 +10845,32 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>280997</t>
+          <t>307021</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>274491</t>
+          <t>301450</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>284450</t>
+          <t>310797</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>97,02%</t>
+          <t>97,14%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>94,77%</t>
+          <t>95,38%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>98,21%</t>
+          <t>98,33%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -10880,32 +10880,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>586163</t>
+          <t>620358</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>577662</t>
+          <t>614004</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>591760</t>
+          <t>625675</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>97,52%</t>
+          <t>97,71%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>96,1%</t>
+          <t>96,71%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>98,45%</t>
+          <t>98,55%</t>
         </is>
       </c>
     </row>
@@ -10923,17 +10923,17 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>311443</t>
+          <t>318845</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>311443</t>
+          <t>318845</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>311443</t>
+          <t>318845</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -10958,17 +10958,17 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>289635</t>
+          <t>316061</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>289635</t>
+          <t>316061</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>289635</t>
+          <t>316061</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -10993,17 +10993,17 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>601077</t>
+          <t>634906</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>601077</t>
+          <t>634906</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>601077</t>
+          <t>634906</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -11040,27 +11040,27 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>35776</t>
+          <t>37055</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>23952</t>
+          <t>25619</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>50242</t>
+          <t>51421</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>6,9%</t>
+          <t>6,98%</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>4,62%</t>
+          <t>4,83%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
@@ -11075,32 +11075,32 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>55632</t>
+          <t>57369</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>44937</t>
+          <t>45768</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>68852</t>
+          <t>70294</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>10,82%</t>
+          <t>10,51%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>8,74%</t>
+          <t>8,39%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>13,39%</t>
+          <t>12,88%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -11110,32 +11110,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>91408</t>
+          <t>94424</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>75798</t>
+          <t>79344</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>110677</t>
+          <t>115976</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>8,85%</t>
+          <t>8,77%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>7,34%</t>
+          <t>7,37%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>10,72%</t>
+          <t>10,77%</t>
         </is>
       </c>
     </row>
@@ -11153,22 +11153,22 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>482614</t>
+          <t>493592</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>468148</t>
+          <t>479226</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>494438</t>
+          <t>505028</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>93,1%</t>
+          <t>93,02%</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
@@ -11178,7 +11178,7 @@
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>95,38%</t>
+          <t>95,17%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -11188,32 +11188,32 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>458690</t>
+          <t>488385</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>445470</t>
+          <t>475460</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>469385</t>
+          <t>499986</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>89,18%</t>
+          <t>89,49%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>86,61%</t>
+          <t>87,12%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>91,26%</t>
+          <t>91,61%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -11223,32 +11223,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>941304</t>
+          <t>981977</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>922035</t>
+          <t>960425</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>956914</t>
+          <t>997057</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>91,15%</t>
+          <t>91,23%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>89,28%</t>
+          <t>89,23%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>92,66%</t>
+          <t>92,63%</t>
         </is>
       </c>
     </row>
@@ -11266,17 +11266,17 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>518390</t>
+          <t>530647</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>518390</t>
+          <t>530647</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>518390</t>
+          <t>530647</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -11301,17 +11301,17 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>514322</t>
+          <t>545754</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>514322</t>
+          <t>545754</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>514322</t>
+          <t>545754</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -11336,17 +11336,17 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>1032712</t>
+          <t>1076401</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>1032712</t>
+          <t>1076401</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>1032712</t>
+          <t>1076401</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -11383,32 +11383,32 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>17671</t>
+          <t>18826</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>12047</t>
+          <t>12636</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>26993</t>
+          <t>28732</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>5,59%</t>
+          <t>5,96%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>3,81%</t>
+          <t>4,0%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>8,54%</t>
+          <t>9,09%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -11418,32 +11418,32 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>22609</t>
+          <t>23609</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>16584</t>
+          <t>17269</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>29677</t>
+          <t>30535</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>6,49%</t>
+          <t>6,64%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>4,76%</t>
+          <t>4,85%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>8,51%</t>
+          <t>8,58%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -11453,32 +11453,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>40280</t>
+          <t>42435</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>31129</t>
+          <t>33371</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>51571</t>
+          <t>54087</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>6,06%</t>
+          <t>6,32%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>4,68%</t>
+          <t>4,97%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>7,76%</t>
+          <t>8,05%</t>
         </is>
       </c>
     </row>
@@ -11496,32 +11496,32 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>298379</t>
+          <t>297167</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>289057</t>
+          <t>287261</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>304003</t>
+          <t>303357</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>94,41%</t>
+          <t>94,04%</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>91,46%</t>
+          <t>90,91%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>96,19%</t>
+          <t>96,0%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -11531,32 +11531,32 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>325959</t>
+          <t>332211</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>318891</t>
+          <t>325285</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>331984</t>
+          <t>338551</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>93,51%</t>
+          <t>93,36%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>91,49%</t>
+          <t>91,42%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>95,24%</t>
+          <t>95,15%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -11566,32 +11566,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>624338</t>
+          <t>629378</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>613047</t>
+          <t>617726</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>633489</t>
+          <t>638442</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>93,94%</t>
+          <t>93,68%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>92,24%</t>
+          <t>91,95%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>95,32%</t>
+          <t>95,03%</t>
         </is>
       </c>
     </row>
@@ -11609,17 +11609,17 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>316050</t>
+          <t>315993</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>316050</t>
+          <t>315993</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>316050</t>
+          <t>315993</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -11644,17 +11644,17 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>348568</t>
+          <t>355820</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>348568</t>
+          <t>355820</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>348568</t>
+          <t>355820</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -11679,17 +11679,17 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>664618</t>
+          <t>671813</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>664618</t>
+          <t>671813</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>664618</t>
+          <t>671813</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -11726,32 +11726,32 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>18463</t>
+          <t>20979</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>11256</t>
+          <t>12604</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>30000</t>
+          <t>33042</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>5,93%</t>
+          <t>5,64%</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>3,62%</t>
+          <t>3,39%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>9,64%</t>
+          <t>8,88%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -11761,32 +11761,32 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>42934</t>
+          <t>47996</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>27027</t>
+          <t>37005</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>61882</t>
+          <t>62292</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>9,03%</t>
+          <t>11,37%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>5,68%</t>
+          <t>8,77%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>13,01%</t>
+          <t>14,76%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -11796,32 +11796,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>61396</t>
+          <t>68975</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>44429</t>
+          <t>54629</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>82092</t>
+          <t>87724</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>7,8%</t>
+          <t>8,69%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>5,64%</t>
+          <t>6,88%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>10,43%</t>
+          <t>11,05%</t>
         </is>
       </c>
     </row>
@@ -11839,32 +11839,32 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>292887</t>
+          <t>350964</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>281350</t>
+          <t>338901</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>300094</t>
+          <t>359339</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>94,07%</t>
+          <t>94,36%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>90,36%</t>
+          <t>91,12%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>96,38%</t>
+          <t>96,61%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -11874,32 +11874,32 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>432784</t>
+          <t>373965</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>413836</t>
+          <t>359669</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>448691</t>
+          <t>384956</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>90,97%</t>
+          <t>88,63%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>86,99%</t>
+          <t>85,24%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>94,32%</t>
+          <t>91,23%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -11909,32 +11909,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>725672</t>
+          <t>724930</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>704976</t>
+          <t>706181</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>742639</t>
+          <t>739276</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>92,2%</t>
+          <t>91,31%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>89,57%</t>
+          <t>88,95%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>94,36%</t>
+          <t>93,12%</t>
         </is>
       </c>
     </row>
@@ -11952,17 +11952,17 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>311350</t>
+          <t>371943</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>311350</t>
+          <t>371943</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>311350</t>
+          <t>371943</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -11987,17 +11987,17 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>475718</t>
+          <t>421961</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>475718</t>
+          <t>421961</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>475718</t>
+          <t>421961</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -12022,17 +12022,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>787068</t>
+          <t>793905</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>787068</t>
+          <t>793905</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>787068</t>
+          <t>793905</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -12069,32 +12069,32 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>5528</t>
+          <t>5736</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>2851</t>
+          <t>2937</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>9798</t>
+          <t>10102</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>3,09%</t>
+          <t>2,79%</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>1,6%</t>
+          <t>1,43%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>5,48%</t>
+          <t>4,91%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -12104,32 +12104,32 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>18641</t>
+          <t>18566</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>13672</t>
+          <t>13759</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>25426</t>
+          <t>24450</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>8,96%</t>
+          <t>8,19%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>6,57%</t>
+          <t>6,07%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>12,22%</t>
+          <t>10,79%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -12139,32 +12139,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>24169</t>
+          <t>24302</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>18053</t>
+          <t>18715</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>31408</t>
+          <t>31060</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>6,25%</t>
+          <t>5,62%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>4,67%</t>
+          <t>4,33%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>8,12%</t>
+          <t>7,19%</t>
         </is>
       </c>
     </row>
@@ -12182,32 +12182,32 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>173214</t>
+          <t>199929</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>168944</t>
+          <t>195563</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>175891</t>
+          <t>202728</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>96,91%</t>
+          <t>97,21%</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>94,52%</t>
+          <t>95,09%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>98,4%</t>
+          <t>98,57%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -12217,32 +12217,32 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>189392</t>
+          <t>208048</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>182607</t>
+          <t>202164</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>194361</t>
+          <t>212855</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>91,04%</t>
+          <t>91,81%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>87,78%</t>
+          <t>89,21%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>93,43%</t>
+          <t>93,93%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -12252,32 +12252,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>362606</t>
+          <t>407976</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>355367</t>
+          <t>401218</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>368722</t>
+          <t>413563</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>93,75%</t>
+          <t>94,38%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>91,88%</t>
+          <t>92,81%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>95,33%</t>
+          <t>95,67%</t>
         </is>
       </c>
     </row>
@@ -12295,17 +12295,17 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>178742</t>
+          <t>205665</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>178742</t>
+          <t>205665</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>178742</t>
+          <t>205665</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -12330,17 +12330,17 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>208033</t>
+          <t>226614</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>208033</t>
+          <t>226614</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>208033</t>
+          <t>226614</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -12365,17 +12365,17 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>386775</t>
+          <t>432278</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>386775</t>
+          <t>432278</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>386775</t>
+          <t>432278</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -12412,32 +12412,32 @@
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>14227</t>
+          <t>13990</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>8946</t>
+          <t>8800</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>21133</t>
+          <t>21346</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>5,28%</t>
+          <t>5,17%</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>3,32%</t>
+          <t>3,25%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>7,84%</t>
+          <t>7,89%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -12447,32 +12447,32 @@
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>18305</t>
+          <t>18453</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>13133</t>
+          <t>13252</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>24284</t>
+          <t>24725</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>7,12%</t>
+          <t>7,0%</t>
         </is>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>5,11%</t>
+          <t>5,02%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>9,45%</t>
+          <t>9,37%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -12482,32 +12482,32 @@
       </c>
       <c r="R19" s="2" t="inlineStr">
         <is>
-          <t>32532</t>
+          <t>32443</t>
         </is>
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>24532</t>
+          <t>25122</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>41076</t>
+          <t>40833</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
         <is>
-          <t>6,18%</t>
+          <t>6,07%</t>
         </is>
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>4,66%</t>
+          <t>4,7%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>7,8%</t>
+          <t>7,64%</t>
         </is>
       </c>
     </row>
@@ -12525,32 +12525,32 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>255409</t>
+          <t>256717</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>248503</t>
+          <t>249361</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>260690</t>
+          <t>261907</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>94,72%</t>
+          <t>94,83%</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>92,16%</t>
+          <t>92,11%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>96,68%</t>
+          <t>96,75%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -12560,32 +12560,32 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>238751</t>
+          <t>245297</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>232772</t>
+          <t>239025</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>243923</t>
+          <t>250498</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>92,88%</t>
+          <t>93,0%</t>
         </is>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>90,55%</t>
+          <t>90,63%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>94,89%</t>
+          <t>94,98%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -12595,32 +12595,32 @@
       </c>
       <c r="R20" s="2" t="inlineStr">
         <is>
-          <t>494160</t>
+          <t>502014</t>
         </is>
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>485616</t>
+          <t>493624</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>502160</t>
+          <t>509335</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
         <is>
-          <t>93,82%</t>
+          <t>93,93%</t>
         </is>
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>92,2%</t>
+          <t>92,36%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>95,34%</t>
+          <t>95,3%</t>
         </is>
       </c>
     </row>
@@ -12638,17 +12638,17 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>269636</t>
+          <t>270707</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>269636</t>
+          <t>270707</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>269636</t>
+          <t>270707</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -12673,17 +12673,17 @@
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>257056</t>
+          <t>263750</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>257056</t>
+          <t>263750</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>257056</t>
+          <t>263750</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -12708,17 +12708,17 @@
       </c>
       <c r="R21" s="2" t="inlineStr">
         <is>
-          <t>526692</t>
+          <t>534457</t>
         </is>
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>526692</t>
+          <t>534457</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>526692</t>
+          <t>534457</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -12755,32 +12755,32 @@
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>50151</t>
+          <t>55382</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>36585</t>
+          <t>40623</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>68259</t>
+          <t>75157</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>8,03%</t>
+          <t>7,7%</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>5,86%</t>
+          <t>5,64%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>10,93%</t>
+          <t>10,44%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -12790,32 +12790,32 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>86078</t>
+          <t>103814</t>
         </is>
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>39556</t>
+          <t>86936</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>120369</t>
+          <t>123912</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
-          <t>10,14%</t>
+          <t>13,45%</t>
         </is>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>4,66%</t>
+          <t>11,26%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>14,17%</t>
+          <t>16,05%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -12825,32 +12825,32 @@
       </c>
       <c r="R22" s="2" t="inlineStr">
         <is>
-          <t>136229</t>
+          <t>159196</t>
         </is>
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>88071</t>
+          <t>135927</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>168947</t>
+          <t>185492</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
         <is>
-          <t>9,24%</t>
+          <t>10,67%</t>
         </is>
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>5,98%</t>
+          <t>9,11%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>11,47%</t>
+          <t>12,43%</t>
         </is>
       </c>
     </row>
@@ -12868,32 +12868,32 @@
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>574128</t>
+          <t>664305</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>556020</t>
+          <t>644530</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>587694</t>
+          <t>679064</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>91,97%</t>
+          <t>92,3%</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>89,07%</t>
+          <t>89,56%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>94,14%</t>
+          <t>94,36%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -12903,32 +12903,32 @@
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>763187</t>
+          <t>668243</t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>728896</t>
+          <t>648145</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>809709</t>
+          <t>685121</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>89,86%</t>
+          <t>86,55%</t>
         </is>
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>85,83%</t>
+          <t>83,95%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>95,34%</t>
+          <t>88,74%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -12938,32 +12938,32 @@
       </c>
       <c r="R23" s="2" t="inlineStr">
         <is>
-          <t>1337315</t>
+          <t>1332548</t>
         </is>
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>1304597</t>
+          <t>1306252</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>1385473</t>
+          <t>1355817</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
         <is>
-          <t>90,76%</t>
+          <t>89,33%</t>
         </is>
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>88,53%</t>
+          <t>87,57%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>94,02%</t>
+          <t>90,89%</t>
         </is>
       </c>
     </row>
@@ -12981,17 +12981,17 @@
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>624279</t>
+          <t>719687</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>624279</t>
+          <t>719687</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>624279</t>
+          <t>719687</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -13016,17 +13016,17 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>849265</t>
+          <t>772057</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>849265</t>
+          <t>772057</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>849265</t>
+          <t>772057</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -13051,17 +13051,17 @@
       </c>
       <c r="R24" s="2" t="inlineStr">
         <is>
-          <t>1473544</t>
+          <t>1491744</t>
         </is>
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>1473544</t>
+          <t>1491744</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>1473544</t>
+          <t>1491744</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -13098,32 +13098,32 @@
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>39744</t>
+          <t>45498</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>18262</t>
+          <t>34258</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>60301</t>
+          <t>59910</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>4,28%</t>
+          <t>5,7%</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>1,97%</t>
+          <t>4,29%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>6,49%</t>
+          <t>7,51%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -13133,32 +13133,32 @@
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>112318</t>
+          <t>123954</t>
         </is>
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>97168</t>
+          <t>109011</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>130631</t>
+          <t>143441</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
         <is>
-          <t>15,65%</t>
+          <t>14,91%</t>
         </is>
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>13,54%</t>
+          <t>13,11%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>18,2%</t>
+          <t>17,25%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -13168,32 +13168,32 @@
       </c>
       <c r="R25" s="2" t="inlineStr">
         <is>
-          <t>152062</t>
+          <t>169452</t>
         </is>
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>94856</t>
+          <t>147254</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>189787</t>
+          <t>189251</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
         <is>
-          <t>9,24%</t>
+          <t>10,4%</t>
         </is>
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>5,76%</t>
+          <t>9,04%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>11,53%</t>
+          <t>11,61%</t>
         </is>
       </c>
     </row>
@@ -13211,32 +13211,32 @@
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>888976</t>
+          <t>752574</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>868419</t>
+          <t>738162</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>910458</t>
+          <t>763814</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t>95,72%</t>
+          <t>94,3%</t>
         </is>
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>93,51%</t>
+          <t>92,49%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>98,03%</t>
+          <t>95,71%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -13246,32 +13246,32 @@
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>605413</t>
+          <t>707377</t>
         </is>
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>587100</t>
+          <t>687890</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>620563</t>
+          <t>722320</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
-          <t>84,35%</t>
+          <t>85,09%</t>
         </is>
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>81,8%</t>
+          <t>82,75%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>86,46%</t>
+          <t>86,89%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -13281,32 +13281,32 @@
       </c>
       <c r="R26" s="2" t="inlineStr">
         <is>
-          <t>1494390</t>
+          <t>1459951</t>
         </is>
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>1456665</t>
+          <t>1440152</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>1551596</t>
+          <t>1482149</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
         <is>
-          <t>90,76%</t>
+          <t>89,6%</t>
         </is>
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>88,47%</t>
+          <t>88,39%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>94,24%</t>
+          <t>90,96%</t>
         </is>
       </c>
     </row>
@@ -13324,17 +13324,17 @@
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>928720</t>
+          <t>798072</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>928720</t>
+          <t>798072</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>928720</t>
+          <t>798072</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -13359,17 +13359,17 @@
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>717731</t>
+          <t>831331</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>717731</t>
+          <t>831331</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>717731</t>
+          <t>831331</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -13394,17 +13394,17 @@
       </c>
       <c r="R27" s="2" t="inlineStr">
         <is>
-          <t>1646452</t>
+          <t>1629403</t>
         </is>
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>1646452</t>
+          <t>1629403</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>1646452</t>
+          <t>1629403</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
@@ -13441,32 +13441,32 @@
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t>187834</t>
+          <t>202972</t>
         </is>
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>144095</t>
+          <t>176467</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>218060</t>
+          <t>233558</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
         <is>
-          <t>5,43%</t>
+          <t>5,75%</t>
         </is>
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>4,17%</t>
+          <t>5,0%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>6,3%</t>
+          <t>6,61%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -13476,32 +13476,32 @@
       </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>365157</t>
+          <t>402803</t>
         </is>
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>293952</t>
+          <t>372575</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>409591</t>
+          <t>438334</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
         <is>
+          <t>10,79%</t>
+        </is>
+      </c>
+      <c r="O28" s="2" t="inlineStr">
+        <is>
           <t>9,98%</t>
         </is>
       </c>
-      <c r="O28" s="2" t="inlineStr">
-        <is>
-          <t>8,03%</t>
-        </is>
-      </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>11,19%</t>
+          <t>11,74%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -13511,32 +13511,32 @@
       </c>
       <c r="R28" s="2" t="inlineStr">
         <is>
-          <t>552991</t>
+          <t>605775</t>
         </is>
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>480796</t>
+          <t>560588</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>614848</t>
+          <t>646768</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
         <is>
-          <t>7,77%</t>
+          <t>8,34%</t>
         </is>
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>6,75%</t>
+          <t>7,72%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>8,64%</t>
+          <t>8,9%</t>
         </is>
       </c>
     </row>
@@ -13554,32 +13554,32 @@
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>3270777</t>
+          <t>3328588</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>3240551</t>
+          <t>3298002</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>3314516</t>
+          <t>3355093</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>94,57%</t>
+          <t>94,25%</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>93,7%</t>
+          <t>93,39%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>95,83%</t>
+          <t>95,0%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -13589,34 +13589,34 @@
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>3295170</t>
+          <t>3330545</t>
         </is>
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>3250736</t>
+          <t>3295014</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>3366375</t>
+          <t>3360773</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
         <is>
+          <t>89,21%</t>
+        </is>
+      </c>
+      <c r="O29" s="2" t="inlineStr">
+        <is>
+          <t>88,26%</t>
+        </is>
+      </c>
+      <c r="P29" s="2" t="inlineStr">
+        <is>
           <t>90,02%</t>
         </is>
       </c>
-      <c r="O29" s="2" t="inlineStr">
-        <is>
-          <t>88,81%</t>
-        </is>
-      </c>
-      <c r="P29" s="2" t="inlineStr">
-        <is>
-          <t>91,97%</t>
-        </is>
-      </c>
       <c r="Q29" s="2" t="inlineStr">
         <is>
           <t>7912</t>
@@ -13624,32 +13624,32 @@
       </c>
       <c r="R29" s="2" t="inlineStr">
         <is>
-          <t>6565947</t>
+          <t>6659134</t>
         </is>
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>6504090</t>
+          <t>6618141</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>6638142</t>
+          <t>6704321</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
         <is>
-          <t>92,23%</t>
+          <t>91,66%</t>
         </is>
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>91,36%</t>
+          <t>91,1%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>93,25%</t>
+          <t>92,28%</t>
         </is>
       </c>
     </row>
@@ -13667,17 +13667,17 @@
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>3458611</t>
+          <t>3531560</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>3458611</t>
+          <t>3531560</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>3458611</t>
+          <t>3531560</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -13702,17 +13702,17 @@
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>3660327</t>
+          <t>3733348</t>
         </is>
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>3660327</t>
+          <t>3733348</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>3660327</t>
+          <t>3733348</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -13737,17 +13737,17 @@
       </c>
       <c r="R30" s="2" t="inlineStr">
         <is>
-          <t>7118938</t>
+          <t>7264909</t>
         </is>
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>7118938</t>
+          <t>7264909</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>7118938</t>
+          <t>7264909</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
